--- a/examples/styles.example.xlsx
+++ b/examples/styles.example.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="516">
   <si>
     <t>name</t>
   </si>
@@ -39,13 +39,7 @@
     <t>nameen</t>
   </si>
   <si>
-    <t>base</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>史詩星海油畫封面/壮大な星海油絵カバー/Epic Star-Sea Opera Canvas</t>
+    <t>太空歌劇_史詩星海油畫封面/スペースオペラ - 壮大な星月夜の油絵カバー/Space Opera - A magnificent oil painting cover of a starry night</t>
   </si>
   <si>
     <t>epic space opera aesthetic, classical oil painting texture, deep navy and gold palette, chiaroscuro, starfield bokeh, majestic scale, formal composition, cinematic lighting, detailed rendering, highres</t>
@@ -57,19 +51,19 @@
     <t>low quality, blurry, jpeg artifacts, text, watermark, logo, signature</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 太空歌劇</t>
-  </si>
-  <si>
-    <t>史詩星海油畫封面</t>
-  </si>
-  <si>
-    <t>壮大な星海油絵カバー</t>
-  </si>
-  <si>
-    <t>Epic Star-Sea Opera Canvas</t>
-  </si>
-  <si>
-    <t>星史檔案線稿/星史アーカイブ線画/Celestial Archive Line Sketch</t>
+    <t>內文插圖風格</t>
+  </si>
+  <si>
+    <t>太空歌劇_史詩星海油畫封面</t>
+  </si>
+  <si>
+    <t>スペースオペラ - 壮大な星月夜の油絵カバー</t>
+  </si>
+  <si>
+    <t>Space Opera - A magnificent oil painting cover of a starry night</t>
+  </si>
+  <si>
+    <t>文學小說_ 讀書會小說_星史檔案線稿/文学小説_ ブッククラブ小説_ スターヒス​​トリーアーカイブ 線画/Literary Fiction_ Book Club Fiction_ Star History Archive Line Drawings</t>
   </si>
   <si>
     <t>monochrome lineart, fine ink lines, cross-hatching, sepia wash, paper texture, low contrast, elegant linework, historical print feel, simple background, highres</t>
@@ -78,19 +72,16 @@
     <t>A restrained interior-illustration treatment with fine monochrome ink lineart, light cross-hatching, sepia wash, paper texture, and low contrast, giving an elegant historical-print feel while remaining readable.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 文學小說 &gt; 讀書會小說</t>
-  </si>
-  <si>
-    <t>星史檔案線稿</t>
-  </si>
-  <si>
-    <t>星史アーカイブ線画</t>
-  </si>
-  <si>
-    <t>Celestial Archive Line Sketch</t>
-  </si>
-  <si>
-    <t>英雄卡通渲染奇幻/英雄セルシェードファンタジー/Heroic Cel-Shaded Fantasy</t>
+    <t>文學小說_ 讀書會小說_星史檔案線稿</t>
+  </si>
+  <si>
+    <t>文学小説_ ブッククラブ小説_ スターヒス​​トリーアーカイブ 線画</t>
+  </si>
+  <si>
+    <t>Literary Fiction_ Book Club Fiction_ Star History Archive Line Drawings</t>
+  </si>
+  <si>
+    <t>日常系戀愛喜劇_英雄卡通渲染奇幻/日常ロマンティックコメディ_ヒーローカートゥーンレンダリングファンタジー/Everyday Romantic Comedy - Hero Cartoon Rendering Fantasy</t>
   </si>
   <si>
     <t>cel shading, stylized realism, painterly sky, volumetric light, soft bloom, vibrant but natural palette, high contrast, clean edges, epic fantasy atmosphere, highres</t>
@@ -99,19 +90,16 @@
     <t>A heroic cel-shaded fantasy treatment blending stylized realism with painterly atmosphere, soft volumetric light, vibrant yet natural colors, and clean epic composition for a legendary adventure cover.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 日常系戀愛喜劇</t>
-  </si>
-  <si>
-    <t>英雄卡通渲染奇幻</t>
-  </si>
-  <si>
-    <t>英雄セルシェードファンタジー</t>
-  </si>
-  <si>
-    <t>Heroic Cel-Shaded Fantasy</t>
-  </si>
-  <si>
-    <t>冒險者鉛筆淡彩/冒険者鉛筆淡彩/Adventurer Pencil Wash</t>
+    <t>日常系戀愛喜劇_英雄卡通渲染奇幻</t>
+  </si>
+  <si>
+    <t>日常ロマンティックコメディ_ヒーローカートゥーンレンダリングファンタジー</t>
+  </si>
+  <si>
+    <t>Everyday Romantic Comedy - Hero Cartoon Rendering Fantasy</t>
+  </si>
+  <si>
+    <t>古典劍與魔法奇幻_冒險者鉛筆淡彩/古典的な剣と魔法のファンタジー - 冒険家ペンシルカラー/Classic sword and sorcery fantasy - Adventurer's pencil color</t>
   </si>
   <si>
     <t>pencil sketch, light watercolor wash, fine lineart, paper grain, soft contrast, muted earthy tones, simple rendering, highres</t>
@@ -120,19 +108,16 @@
     <t>A restrained adventurer pencil-and-wash treatment with fine lineart, light watercolor, paper grain, muted earthy tones, and soft contrast for readable interior fantasy illustrations.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 古典劍與魔法奇幻</t>
-  </si>
-  <si>
-    <t>冒險者鉛筆淡彩</t>
-  </si>
-  <si>
-    <t>冒険者鉛筆淡彩</t>
-  </si>
-  <si>
-    <t>Adventurer Pencil Wash</t>
-  </si>
-  <si>
-    <t>明亮俏皮卡通渲染/明るい陽気カートゥーンレンダー/Bright Playful Cartoon Render</t>
+    <t>古典劍與魔法奇幻_冒險者鉛筆淡彩</t>
+  </si>
+  <si>
+    <t>古典的な剣と魔法のファンタジー - 冒険家ペンシルカラー</t>
+  </si>
+  <si>
+    <t>Classic sword and sorcery fantasy - Adventurer's pencil color</t>
+  </si>
+  <si>
+    <t>史詩太空歌劇_明亮俏皮卡通渲染/壮大なスペースオペラ - 明るく遊び心のある漫画風レンダリング/An epic space opera - with bright and playful cartoon-style renderings</t>
   </si>
   <si>
     <t>bright cartoon rendering, saturated primary colors, rounded shapes, soft specular highlights, clean thick outlines, cheerful atmosphere, 3D-rendered feel, highres</t>
@@ -141,19 +126,16 @@
     <t>A bright playful cartoon-render treatment with saturated primary colors, rounded shapes, thick clean outlines, soft highlights, and a cheerful 3D-rendered feel for a family-friendly cover.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 史詩太空歌劇</t>
-  </si>
-  <si>
-    <t>明亮俏皮卡通渲染</t>
-  </si>
-  <si>
-    <t>明るい陽気カートゥーンレンダー</t>
-  </si>
-  <si>
-    <t>Bright Playful Cartoon Render</t>
-  </si>
-  <si>
-    <t>粗線簡潔卡通/太線シンプルカートゥーン/Bold Simple Cartoon Line</t>
+    <t>史詩太空歌劇_明亮俏皮卡通渲染</t>
+  </si>
+  <si>
+    <t>壮大なスペースオペラ - 明るく遊び心のある漫画風レンダリング</t>
+  </si>
+  <si>
+    <t>An epic space opera - with bright and playful cartoon-style renderings</t>
+  </si>
+  <si>
+    <t>史詩奇幻_ 高奇幻_粗線簡潔卡通/壮大なファンタジー_ハイファンタジー_太線で描かれたシンプルな漫画/Epic fantasy_High fantasy_Simple comic drawn with thick lines</t>
   </si>
   <si>
     <t>bold outlines, flat colors, simple shapes, high readability, minimal shading, clean white background feel, cheerful palette, highres</t>
@@ -162,19 +144,16 @@
     <t>A bold and simple cartoon-line treatment with flat colors, thick outlines, minimal shading, high readability, and a cheerful palette for interior playful illustrations.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 史詩奇幻 &gt; 高奇幻</t>
-  </si>
-  <si>
-    <t>粗線簡潔卡通</t>
-  </si>
-  <si>
-    <t>太線シンプルカートゥーン</t>
-  </si>
-  <si>
-    <t>Bold Simple Cartoon Line</t>
-  </si>
-  <si>
-    <t>古典劍與魔法油畫/古典剣と魔法の油絵/Classical Sword-and-Sorcery Oil</t>
+    <t>史詩奇幻_ 高奇幻_粗線簡潔卡通</t>
+  </si>
+  <si>
+    <t>壮大なファンタジー_ハイファンタジー_太線で描かれたシンプルな漫画</t>
+  </si>
+  <si>
+    <t>Epic fantasy_High fantasy_Simple comic drawn with thick lines</t>
+  </si>
+  <si>
+    <t>生物收集冒險_古典劍與魔法油畫/クリーチャーコレクションアドベンチャー - クラシックソードアンドマジック油絵/Creature Collection Adventure - Classic Sword and Magic Oil Painting</t>
   </si>
   <si>
     <t>classical fantasy oil painting, impasto texture, earthy palette, dramatic chiaroscuro, ornate detail, old-world atmosphere, fine brushwork, highres</t>
@@ -183,19 +162,16 @@
     <t>A classical sword-and-sorcery oil-painting treatment with impasto texture, earthy tones, dramatic chiaroscuro, ornate detail, and an old-world atmosphere for a foundational fantasy cover.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 生物收集冒險</t>
-  </si>
-  <si>
-    <t>古典劍與魔法油畫</t>
-  </si>
-  <si>
-    <t>古典剣と魔法の油絵</t>
-  </si>
-  <si>
-    <t>Classical Sword-and-Sorcery Oil</t>
-  </si>
-  <si>
-    <t>東西融合雅緻線稿/東西融合優雅線画/Elegant East-West Line Draft</t>
+    <t>生物收集冒險_古典劍與魔法油畫</t>
+  </si>
+  <si>
+    <t>クリーチャーコレクションアドベンチャー - クラシックソードアンドマジック油絵</t>
+  </si>
+  <si>
+    <t>Creature Collection Adventure - Classic Sword and Magic Oil Painting</t>
+  </si>
+  <si>
+    <t>全年齡卡通冒險_東西融合雅緻線稿/全年齢対象のカートゥーンアドベンチャー - 東西の美学を融合させたエレガントな線画/A cartoon adventure for all ages - elegant line art blending Eastern and Western aesthetics.</t>
   </si>
   <si>
     <t>elegant lineart, fine ink lines, cross-hatching, light ink wash, paper texture, low saturation, delicate details, fusion of eastern and western aesthetics, highres</t>
@@ -204,19 +180,16 @@
     <t>An elegant east-west line-draft treatment with fine ink lines, light cross-hatching, pale ink wash, paper texture, and delicate fusion aesthetics for interior classic fantasy illustrations.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 全年齡卡通冒險</t>
-  </si>
-  <si>
-    <t>東西融合雅緻線稿</t>
-  </si>
-  <si>
-    <t>東西融合優雅線画</t>
-  </si>
-  <si>
-    <t>Elegant East-West Line Draft</t>
-  </si>
-  <si>
-    <t>太空歌劇黃金時代插畫/宇宙歌劇黄金時代イラスト/Space Opera Golden-Age Illustration</t>
+    <t>全年齡卡通冒險_東西融合雅緻線稿</t>
+  </si>
+  <si>
+    <t>全年齢対象のカートゥーンアドベンチャー - 東西の美学を融合させたエレガントな線画</t>
+  </si>
+  <si>
+    <t>A cartoon adventure for all ages - elegant line art blending Eastern and Western aesthetics.</t>
+  </si>
+  <si>
+    <t>奇幻懸疑_ 推理_太空歌劇黃金時代插畫/ファンタジー・サスペンス・ミステリー・スペースオペラ黄金時代のイラストレーション/Illustrations from the Golden Age of Fantasy, Suspense, Mystery, and Space Opera</t>
   </si>
   <si>
     <t>space opera aesthetic, golden-age illustration influence, rich jewel tones, soft airbrush shading, elegant linework, cosmic atmosphere, dramatic lighting, highres</t>
@@ -225,19 +198,16 @@
     <t>A space-opera treatment influenced by golden-age illustration, featuring rich jewel tones, soft airbrush shading, elegant linework, and a dramatic cosmic atmosphere for an epic cover.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 奇幻懸疑 &gt; 推理</t>
-  </si>
-  <si>
-    <t>太空歌劇黃金時代插畫</t>
-  </si>
-  <si>
-    <t>宇宙歌劇黄金時代イラスト</t>
-  </si>
-  <si>
-    <t>Space Opera Golden-Age Illustration</t>
-  </si>
-  <si>
-    <t>精緻鋼筆淡彩/精密ペン淡彩/Precision Pen and Pale Tint</t>
+    <t>奇幻懸疑_ 推理_太空歌劇黃金時代插畫</t>
+  </si>
+  <si>
+    <t>ファンタジー・サスペンス・ミステリー・スペースオペラ黄金時代のイラストレーション</t>
+  </si>
+  <si>
+    <t>Illustrations from the Golden Age of Fantasy, Suspense, Mystery, and Space Opera</t>
+  </si>
+  <si>
+    <t>東方異世界史詩_精緻鋼筆淡彩/異世界の東洋を舞台にした壮大な物語 ― 精緻なペンとインクの水彩画/An epic tale set in an otherworldly Orient — depicted with exquisite pen and ink watercolors.</t>
   </si>
   <si>
     <t>precise pen lineart, fine hatching, pale watercolor tint, paper texture, low contrast, elegant minimal rendering, high readability, highres</t>
@@ -246,19 +216,16 @@
     <t>A precision pen-and-pale-tint treatment with fine hatching, light watercolor, paper texture, low contrast, and elegant minimal rendering for interior space-opera illustrations.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 東方異世界史詩</t>
-  </si>
-  <si>
-    <t>精緻鋼筆淡彩</t>
-  </si>
-  <si>
-    <t>精密ペン淡彩</t>
-  </si>
-  <si>
-    <t>Precision Pen and Pale Tint</t>
-  </si>
-  <si>
-    <t>東方史詩重彩/東洋史詩重彩/Oriental Epic Gouache</t>
+    <t>東方異世界史詩_精緻鋼筆淡彩</t>
+  </si>
+  <si>
+    <t>異世界の東洋を舞台にした壮大な物語 ― 精緻なペンとインクの水彩画</t>
+  </si>
+  <si>
+    <t>An epic tale set in an otherworldly Orient — depicted with exquisite pen and ink watercolors.</t>
+  </si>
+  <si>
+    <t>空靈奇幻角色扮演_東方史詩重彩/幻想的なファンタジーロールプレイング - フルカラーで描かれる東洋の叙事詩/A fantastical role-playing game - an Eastern epic depicted in full color.</t>
   </si>
   <si>
     <t>oriental gouache painting, fine brushwork, layered mineral pigments, majestic composition, elegant linework, muted gold and azurite tones, epic atmosphere, highres</t>
@@ -267,19 +234,16 @@
     <t>An oriental epic gouache treatment with fine brushwork, layered mineral pigments, majestic composition, elegant linework, and muted gold-and-azurite tones for a grand otherworldly cover.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 空靈奇幻角色扮演</t>
-  </si>
-  <si>
-    <t>東方史詩重彩</t>
-  </si>
-  <si>
-    <t>東洋史詩重彩</t>
-  </si>
-  <si>
-    <t>Oriental Epic Gouache</t>
-  </si>
-  <si>
-    <t>墨線淡彩/墨線淡彩/Ink Line and Subtle Color</t>
+    <t>空靈奇幻角色扮演_東方史詩重彩</t>
+  </si>
+  <si>
+    <t>幻想的なファンタジーロールプレイング - フルカラーで描かれる東洋の叙事詩</t>
+  </si>
+  <si>
+    <t>A fantastical role-playing game - an Eastern epic depicted in full color.</t>
+  </si>
+  <si>
+    <t>科幻_ 推想小說_墨線淡彩/サイエンス・フィクション_スペキュラティブ・フィクション_インクの線と淡い色彩/Science fiction, speculative fiction, ink lines and soft colors</t>
   </si>
   <si>
     <t>ink lineart, fine brush texture, subtle mineral color accents, paper grain, low saturation, elegant restraint, high readability, highres</t>
@@ -288,16 +252,16 @@
     <t>An ink-line-and-subtle-color treatment with fine brush texture, light mineral accents, paper grain, low saturation, and elegant restraint for interior otherworldly illustrations.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 科幻 &gt; 推想小說</t>
-  </si>
-  <si>
-    <t>墨線淡彩</t>
-  </si>
-  <si>
-    <t>Ink Line and Subtle Color</t>
-  </si>
-  <si>
-    <t>現代濃彩戲劇渲染/現代リッチセルシェード/Modern Rich Cel-Shaded Drama</t>
+    <t>科幻_ 推想小說_墨線淡彩</t>
+  </si>
+  <si>
+    <t>サイエンス・フィクション_スペキュラティブ・フィクション_インクの線と淡い色彩</t>
+  </si>
+  <si>
+    <t>Science fiction, speculative fiction, ink lines and soft colors</t>
+  </si>
+  <si>
+    <t>英雄奇幻冒險_現代濃彩戲劇渲染/英雄的なファンタジーアドベンチャー - 現代の鮮やかなドラマ/A heroic fantasy adventure - a vibrant modern drama</t>
   </si>
   <si>
     <t>modern cel shading, rich gradient lighting, metallic highlights, dramatic contrast, glossy finish, detailed rendering, high saturation accents, highres</t>
@@ -306,19 +270,16 @@
     <t>A modern rich cel-shaded treatment with gradient lighting, metallic highlights, dramatic contrast, glossy finish, and detailed rendering for a dramatic urban-fantasy cover.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 英雄奇幻冒險</t>
-  </si>
-  <si>
-    <t>現代濃彩戲劇渲染</t>
-  </si>
-  <si>
-    <t>現代リッチセルシェード</t>
-  </si>
-  <si>
-    <t>Modern Rich Cel-Shaded Drama</t>
-  </si>
-  <si>
-    <t>乾淨線稿局部上色/クリーン線画スポットカラー/Clean Line and Spot Color</t>
+    <t>英雄奇幻冒險_現代濃彩戲劇渲染</t>
+  </si>
+  <si>
+    <t>英雄的なファンタジーアドベンチャー - 現代の鮮やかなドラマ</t>
+  </si>
+  <si>
+    <t>A heroic fantasy adventure - a vibrant modern drama</t>
+  </si>
+  <si>
+    <t>宮廷謎案_ 歷史戀愛_乾淨線稿局部上色/パレスミステリー_歴史ロマンス_ 線画に部分的な着色を施したシンプルなイラスト/Palace Mystery_Historical Romance_Simple illustration with partial coloring on line art</t>
   </si>
   <si>
     <t>clean lineart, spot color accents, minimal shading, white background feel, high readability, crisp edges, low visual noise, highres</t>
@@ -327,19 +288,16 @@
     <t>A clean line-and-spot-color treatment with crisp edges, minimal shading, low visual noise, and high readability for interior urban-fantasy illustrations.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 宮廷謎案 &gt; 歷史戀愛</t>
-  </si>
-  <si>
-    <t>乾淨線稿局部上色</t>
-  </si>
-  <si>
-    <t>クリーン線画スポットカラー</t>
-  </si>
-  <si>
-    <t>Clean Line and Spot Color</t>
-  </si>
-  <si>
-    <t>空靈水彩幻想/幻想的水彩ファンタジー/Ethereal Watercolor Fantasy</t>
+    <t>宮廷謎案_ 歷史戀愛_乾淨線稿局部上色</t>
+  </si>
+  <si>
+    <t>パレスミステリー_歴史ロマンス_ 線画に部分的な着色を施したシンプルなイラスト</t>
+  </si>
+  <si>
+    <t>Palace Mystery_Historical Romance_Simple illustration with partial coloring on line art</t>
+  </si>
+  <si>
+    <t>恐怖_ 哥德_空靈水彩幻想/ホラー_ゴシック_幻想的な水彩ファンタジー/Horror, Gothic, and fantastical watercolor fantasy</t>
   </si>
   <si>
     <t>ethereal watercolor, flowing linework, pale iridescent washes, soft diffusion, fantasy atmosphere, delicate brush texture, highres</t>
@@ -348,19 +306,16 @@
     <t>An ethereal watercolor-fantasy treatment with flowing linework, pale iridescent washes, soft diffusion, delicate brush texture, and a dreamlike fantasy atmosphere for a signature RPG cover.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 恐怖 &gt; 哥德</t>
-  </si>
-  <si>
-    <t>空靈水彩幻想</t>
-  </si>
-  <si>
-    <t>幻想的水彩ファンタジー</t>
-  </si>
-  <si>
-    <t>Ethereal Watercolor Fantasy</t>
-  </si>
-  <si>
-    <t>細鋼筆水彩淡染/細ペン水彩淡彩/Fine Pen and Watercolor Wash</t>
+    <t>恐怖_ 哥德_空靈水彩幻想</t>
+  </si>
+  <si>
+    <t>ホラー_ゴシック_幻想的な水彩ファンタジー</t>
+  </si>
+  <si>
+    <t>Horror, Gothic, and fantastical watercolor fantasy</t>
+  </si>
+  <si>
+    <t>校園黨爭_ 群像劇_細鋼筆水彩淡染/キャンパス内の派閥争い_群像劇_細密なペン画による水彩画/Factional struggles on campus - an ensemble drama - watercolor paintings with detailed pen and ink.</t>
   </si>
   <si>
     <t>fine pen lineart, light watercolor wash, paper texture, soft gradients, low contrast, elegant fantasy rendering, highres</t>
@@ -369,19 +324,16 @@
     <t>A fine pen-and-watercolor treatment with light washes, paper texture, soft gradients, low contrast, and elegant fantasy rendering for interior RPG illustrations.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 校園黨爭 &gt; 群像劇</t>
-  </si>
-  <si>
-    <t>細鋼筆水彩淡染</t>
-  </si>
-  <si>
-    <t>細ペン水彩淡彩</t>
-  </si>
-  <si>
-    <t>Fine Pen and Watercolor Wash</t>
-  </si>
-  <si>
-    <t>歡樂圓潤卡通光影/楽しい丸みカートゥーン/Cheerful Rounded Cartoon Shading</t>
+    <t>校園黨爭_ 群像劇_細鋼筆水彩淡染</t>
+  </si>
+  <si>
+    <t>キャンパス内の派閥争い_群像劇_細密なペン画による水彩画</t>
+  </si>
+  <si>
+    <t>Factional struggles on campus - an ensemble drama - watercolor paintings with detailed pen and ink.</t>
+  </si>
+  <si>
+    <t>浪漫小說_ 當代浪漫_歡樂圓潤卡通光影/ロマンス小説_現代ロマンス_楽しくて丸みのある漫画の光と影/Romance novel_Modern romance_The light and shadow of a fun and rounded comic</t>
   </si>
   <si>
     <t>rounded cartoon shading, bright saturated colors, soft gradients, clean thick outlines, friendly atmosphere, glossy highlights, highres</t>
@@ -390,19 +342,16 @@
     <t>A cheerful rounded cartoon-shading treatment with bright saturated colors, soft gradients, thick clean outlines, glossy highlights, and a friendly atmosphere for a creature-collection cover.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 浪漫小說 &gt; 當代浪漫</t>
-  </si>
-  <si>
-    <t>歡樂圓潤卡通光影</t>
-  </si>
-  <si>
-    <t>楽しい丸みカートゥーン</t>
-  </si>
-  <si>
-    <t>Cheerful Rounded Cartoon Shading</t>
-  </si>
-  <si>
-    <t>簡潔平塗卡通/シンプル平塗カートゥーン/Simple Flat Cartoon Line</t>
+    <t>浪漫小說_ 當代浪漫_歡樂圓潤卡通光影</t>
+  </si>
+  <si>
+    <t>ロマンス小説_現代ロマンス_楽しくて丸みのある漫画の光と影</t>
+  </si>
+  <si>
+    <t>Romance novel_Modern romance_The light and shadow of a fun and rounded comic</t>
+  </si>
+  <si>
+    <t>現代都市奇幻_簡潔平塗卡通/現代都市ファンタジー - シンプルなフラットカートゥーンスタイル/Modern urban fantasy - simple flat cartoon style</t>
   </si>
   <si>
     <t>simple flat colors, bold clean outlines, minimal shading, cheerful palette, high readability, white background feel, highres</t>
@@ -411,19 +360,16 @@
     <t>A simple flat-cartoon treatment with bold outlines, minimal shading, a cheerful palette, and high readability for interior creature-collection illustrations.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 現代都市奇幻</t>
-  </si>
-  <si>
-    <t>簡潔平塗卡通</t>
-  </si>
-  <si>
-    <t>シンプル平塗カートゥーン</t>
-  </si>
-  <si>
-    <t>Simple Flat Cartoon Line</t>
-  </si>
-  <si>
-    <t>冷峻賽博科技黑色/冷徹サイバーテックノワール/Cold Cyberpunk Tech Noir</t>
+    <t>現代都市奇幻_簡潔平塗卡通</t>
+  </si>
+  <si>
+    <t>現代都市ファンタジー - シンプルなフラットカートゥーンスタイル</t>
+  </si>
+  <si>
+    <t>Modern urban fantasy - simple flat cartoon style</t>
+  </si>
+  <si>
+    <t>都市奇幻_冷峻賽博科技黑色/アーバンファンタジー_クールなサイバーテックブラック/Urban Fantasy_Cool Cybertech Black</t>
   </si>
   <si>
     <t>cold cyberpunk aesthetic, high contrast, neon rim light, tech texture, muted dark palette, film grain, sharp highlights, futuristic atmosphere, highres</t>
@@ -432,19 +378,16 @@
     <t>A cold cyberpunk tech-noir treatment with high contrast, neon rim light, tech texture, muted dark palette, film grain, and sharp highlights for a futuristic cover.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 都市奇幻</t>
-  </si>
-  <si>
-    <t>冷峻賽博科技黑色</t>
-  </si>
-  <si>
-    <t>冷徹サイバーテックノワール</t>
-  </si>
-  <si>
-    <t>Cold Cyberpunk Tech Noir</t>
-  </si>
-  <si>
-    <t>技術單色機械線稿/テクニカルモノクロメカ線画/Technical Monochrome Mech Draft</t>
+    <t>都市奇幻_冷峻賽博科技黑色</t>
+  </si>
+  <si>
+    <t>アーバンファンタジー_クールなサイバーテックブラック</t>
+  </si>
+  <si>
+    <t>Urban Fantasy_Cool Cybertech Black</t>
+  </si>
+  <si>
+    <t>舒適奇幻_ 溫馨奇幻_技術單色機械線稿/快適なファンタジー_ 温かいファンタジー_ テクニカルモノクロームメカニカルラインアート/Comfortable Fantasy_ Warm Fantasy_ Technical Monochrome Mechanical Line Art</t>
   </si>
   <si>
     <t>technical lineart, monochrome blue tone, fine mechanical lines, low saturation, precise diagram feel, simple background, high readability, highres</t>
@@ -453,19 +396,16 @@
     <t>A technical monochrome mech-draft treatment with fine mechanical lines, low-saturation blue tones, precise diagram feel, and high readability for interior cyberpunk illustrations.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 舒適奇幻 &gt; 溫馨奇幻</t>
-  </si>
-  <si>
-    <t>技術單色機械線稿</t>
-  </si>
-  <si>
-    <t>テクニカルモノクロメカ線画</t>
-  </si>
-  <si>
-    <t>Technical Monochrome Mech Draft</t>
-  </si>
-  <si>
-    <t>心理高反差戲劇/心理高コントラストドラマ/Psychological High-Contrast Drama</t>
+    <t>舒適奇幻_ 溫馨奇幻_技術單色機械線稿</t>
+  </si>
+  <si>
+    <t>快適なファンタジー_ 温かいファンタジー_ テクニカルモノクロームメカニカルラインアート</t>
+  </si>
+  <si>
+    <t>Comfortable Fantasy_ Warm Fantasy_ Technical Monochrome Mechanical Line Art</t>
+  </si>
+  <si>
+    <t>慢生活_ 職人奇幻_心理高反差戲劇/スローリビング_職人の幻想_心理的ハイコントラストドラマ/Slow Living: The Craftsman's Illusion - A Psychological High-Contrast Drama</t>
   </si>
   <si>
     <t>high-contrast dramatic lighting, painterly cel shading, intense color accents, psychological atmosphere, sharp shadows, glossy finish, highres</t>
@@ -474,19 +414,16 @@
     <t>A psychological high-contrast dramatic treatment with painterly cel shading, intense color accents, sharp shadows, glossy finish, and an unsettling atmosphere for a mecha-psychodrama cover.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 慢生活 &gt; 職人奇幻</t>
-  </si>
-  <si>
-    <t>心理高反差戲劇</t>
-  </si>
-  <si>
-    <t>心理高コントラストドラマ</t>
-  </si>
-  <si>
-    <t>Psychological High-Contrast Drama</t>
-  </si>
-  <si>
-    <t>乾淨漫畫線稿網點/クリーン漫画線画トーン/Clean Comic Line with Screentone</t>
+    <t>慢生活_ 職人奇幻_心理高反差戲劇</t>
+  </si>
+  <si>
+    <t>スローリビング_職人の幻想_心理的ハイコントラストドラマ</t>
+  </si>
+  <si>
+    <t>Slow Living: The Craftsman's Illusion - A Psychological High-Contrast Drama</t>
+  </si>
+  <si>
+    <t>機甲心理劇_乾淨漫畫線稿網點/メカサイコドラマ_クリーンコミックラインアートスクリーン/Mecha Psychodrama_Clean Comic Line Art Screen</t>
   </si>
   <si>
     <t>clean comic lineart, screentone shading, fine hatching, monochrome with spot color, high readability, crisp edges, highres</t>
@@ -495,19 +432,16 @@
     <t>A clean comic-line treatment with screentone shading, fine hatching, monochrome base with spot color, crisp edges, and high readability for interior mecha-psychodrama illustrations.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 機甲心理劇</t>
-  </si>
-  <si>
-    <t>乾淨漫畫線稿網點</t>
-  </si>
-  <si>
-    <t>クリーン漫画線画トーン</t>
-  </si>
-  <si>
-    <t>Clean Comic Line with Screentone</t>
-  </si>
-  <si>
-    <t>華麗惡役千金肖像/華麗悪役令嬢ポートレート/Gilded Villainess Portrait</t>
+    <t>機甲心理劇_乾淨漫畫線稿網點</t>
+  </si>
+  <si>
+    <t>メカサイコドラマ_クリーンコミックラインアートスクリーン</t>
+  </si>
+  <si>
+    <t>Mecha Psychodrama_Clean Comic Line Art Screen</t>
+  </si>
+  <si>
+    <t>賽博龐克科技黑色_華麗惡役千金肖像/サイバーパンク・テクノロジー・ブラック - 魅惑的な悪女の肖像/Cyberpunk Technology Black - Portrait of a Captivating Femme Fatale</t>
   </si>
   <si>
     <t>gold ornamentation, ornate frame, rich jewel tones, velvet texture, dramatic spotlight, glossy highlights, regal atmosphere, elegant lineart, high contrast, highres</t>
@@ -516,19 +450,16 @@
     <t>A gilded villainess-portrait treatment with ornate gold detailing, rich jewel tones, velvet textures, dramatic spotlight, and glossy highlights for a regal, indulgent cover.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 賽博龐克科技黑色</t>
-  </si>
-  <si>
-    <t>華麗惡役千金肖像</t>
-  </si>
-  <si>
-    <t>華麗悪役令嬢ポートレート</t>
-  </si>
-  <si>
-    <t>Gilded Villainess Portrait</t>
-  </si>
-  <si>
-    <t>蕾絲淡彩線稿/レース淡彩線画/Lace and Pastel Lineart</t>
+    <t>賽博龐克科技黑色_華麗惡役千金肖像</t>
+  </si>
+  <si>
+    <t>サイバーパンク・テクノロジー・ブラック - 魅惑的な悪女の肖像</t>
+  </si>
+  <si>
+    <t>Cyberpunk Technology Black - Portrait of a Captivating Femme Fatale</t>
+  </si>
+  <si>
+    <t>轉生惡役千金_ 宮廷戀愛_蕾絲淡彩線稿/悪役令嬢に転生した～ロイヤルロマンス～ - レースとパステルの線画/Reincarnated as a Villainess ~Royal Romance~ - Lace and Pastel Line Drawings</t>
   </si>
   <si>
     <t>delicate lace patterns, fine lineart, pastel tint, soft shading, rose motifs, paper texture, low contrast, elegant restraint, high readability, highres</t>
@@ -537,19 +468,16 @@
     <t>A delicate lace-and-pastel lineart treatment with fine detailing, soft shading, rose motifs, paper texture, and low contrast for readable interior court-romance illustrations.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 轉生惡役千金 &gt; 宮廷戀愛</t>
-  </si>
-  <si>
-    <t>蕾絲淡彩線稿</t>
-  </si>
-  <si>
-    <t>レース淡彩線画</t>
-  </si>
-  <si>
-    <t>Lace and Pastel Lineart</t>
-  </si>
-  <si>
-    <t>柔焦日常戀愛/ソフトフォーカス日常ラブコメ/Soft-Focus Daily Romance</t>
+    <t>轉生惡役千金_ 宮廷戀愛_蕾絲淡彩線稿</t>
+  </si>
+  <si>
+    <t>悪役令嬢に転生した～ロイヤルロマンス～ - レースとパステルの線画</t>
+  </si>
+  <si>
+    <t>Reincarnated as a Villainess ~Royal Romance~ - Lace and Pastel Line Drawings</t>
+  </si>
+  <si>
+    <t>驚悚_ 懸疑_ 犯罪_柔焦日常戀愛/スリラー、サスペンス、犯罪、ソフトフォーカスな日常ロマンス/Thriller, suspense, crime, soft-focus slice-of-life romance</t>
   </si>
   <si>
     <t>soft focus, pastel palette, gentle gradient lighting, airy atmosphere, clean lineart, subtle blush, warm ambient light, delicate rendering, highres</t>
@@ -558,19 +486,16 @@
     <t>A soft-focus daily-romance treatment with pastel tones, gentle gradients, airy atmosphere, and delicate clean lineart for a gentle, intimate cover.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; 驚悚 &gt; 懸疑 &gt; 犯罪</t>
-  </si>
-  <si>
-    <t>柔焦日常戀愛</t>
-  </si>
-  <si>
-    <t>ソフトフォーカス日常ラブコメ</t>
-  </si>
-  <si>
-    <t>Soft-Focus Daily Romance</t>
-  </si>
-  <si>
-    <t>淡彩日常切片/淡彩スライス・オブ・ライフ/Light Wash Slice-of-Life</t>
+    <t>驚悚_ 懸疑_ 犯罪_柔焦日常戀愛</t>
+  </si>
+  <si>
+    <t>スリラー、サスペンス、犯罪、ソフトフォーカスな日常ロマンス</t>
+  </si>
+  <si>
+    <t>Thriller, suspense, crime, soft-focus slice-of-life romance</t>
+  </si>
+  <si>
+    <t>VR遊戲_ 虛擬世界_淡彩日常切片/VRゲーム_仮想世界_淡い色の日常の断片/VR Game_Virtual World_Fragments of Everyday Life in Pale Colors</t>
   </si>
   <si>
     <t>pale watercolor wash, light lineart, soft contrast, paper grain, muted pastel, simple background feel, gentle expressions, high readability, highres</t>
@@ -579,19 +504,16 @@
     <t>A light-wash slice-of-life treatment with pale watercolor, soft lineart, paper grain, and muted pastel tones for quiet, readable interior romance scenes.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格 &gt; VR遊戲 &gt; 虛擬世界</t>
-  </si>
-  <si>
-    <t>淡彩日常切片</t>
-  </si>
-  <si>
-    <t>淡彩スライス・オブ・ライフ</t>
-  </si>
-  <si>
-    <t>Light Wash Slice-of-Life</t>
-  </si>
-  <si>
-    <t>閃耀群像競演/ルミナス群像劇/Luminous Ensemble Cast</t>
+    <t>VR遊戲_ 虛擬世界_淡彩日常切片</t>
+  </si>
+  <si>
+    <t>VRゲーム_仮想世界_淡い色の日常の断片</t>
+  </si>
+  <si>
+    <t>VR Game_Virtual World_Fragments of Everyday Life in Pale Colors</t>
+  </si>
+  <si>
+    <t>浪漫奇幻_ 浪漫小說_閃耀群像競演/ロマンティックファンタジー_ロマンティック小説_華麗なるアンサンブルパフォーマンス/Romantic Fantasy_Romantic Novel_Magnificent Ensemble Performance</t>
   </si>
   <si>
     <t>glossy finish, vibrant gradient lighting, multiple focal points, dynamic group composition, saturated accent colors, clean edges, polished rendering, high energy, highres</t>
@@ -600,19 +522,16 @@
     <t>A luminous ensemble-cast treatment with glossy finish, vibrant gradient lighting, dynamic group composition, and saturated accent colors for a lively, competitive cover.</t>
   </si>
   <si>
-    <t>內文插圖風格 ,內文插圖風格&gt; 浪漫奇幻 &gt; 浪漫小說</t>
-  </si>
-  <si>
-    <t>閃耀群像競演</t>
-  </si>
-  <si>
-    <t>ルミナス群像劇</t>
-  </si>
-  <si>
-    <t>Luminous Ensemble Cast</t>
-  </si>
-  <si>
-    <t>俐落角色線稿局部色調/Crispキャラ線画スポットトーン/Crisp Character Line and Spot Tone</t>
+    <t>浪漫奇幻_ 浪漫小說_閃耀群像競演</t>
+  </si>
+  <si>
+    <t>ロマンティックファンタジー_ロマンティック小説_華麗なるアンサンブルパフォーマンス</t>
+  </si>
+  <si>
+    <t>Romantic Fantasy_Romantic Novel_Magnificent Ensemble Performance</t>
+  </si>
+  <si>
+    <t>太空歌劇_俐落角色線稿局部色調/スペースオペラ - 部分的なトーンを用いた洗練されたキャラクターラインアート/Space Opera - Sophisticated character line art with partial tones</t>
   </si>
   <si>
     <t>clean character lineart, flat base colors, spot tone accents, minimal shading, white breathing space, crisp expressions, high readability, highres</t>
@@ -621,19 +540,19 @@
     <t>A crisp character-line-and-spot-tone treatment with flat base colors, minimal shading, white breathing space, and crisp expressions for clear, energetic interior group scenes.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 太空歌劇</t>
-  </si>
-  <si>
-    <t>俐落角色線稿局部色調</t>
-  </si>
-  <si>
-    <t>Crispキャラ線画スポットトーン</t>
-  </si>
-  <si>
-    <t>Crisp Character Line and Spot Tone</t>
-  </si>
-  <si>
-    <t>氛圍線索光影/ムーディ手がかりライト/Moody Clue-Lit Frame</t>
+    <t>封面藝術風格</t>
+  </si>
+  <si>
+    <t>太空歌劇_俐落角色線稿局部色調</t>
+  </si>
+  <si>
+    <t>スペースオペラ - 部分的なトーンを用いた洗練されたキャラクターラインアート</t>
+  </si>
+  <si>
+    <t>Space Opera - Sophisticated character line art with partial tones</t>
+  </si>
+  <si>
+    <t>文學小說_ 讀書會小說_氛圍線索光影/文学小説_ ブッククラブ小説_ 雰囲気の手がかりと光と影/Literary Fiction_ Book Club Fiction_ Clues to Atmosphere, Light and Shadow</t>
   </si>
   <si>
     <t>moody lighting, selective spotlight, deep shadows, muted cool palette, subtle texture, suspenseful atmosphere, sharp focal contrast, cinematic framing, highres</t>
@@ -642,19 +561,16 @@
     <t>A moody clue-lit frame treatment with selective spotlight, deep shadows, muted cool tones, subtle texture, and sharp focal contrast for a suspenseful cover.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 文學小說 &gt; 讀書會小說</t>
-  </si>
-  <si>
-    <t>氛圍線索光影</t>
-  </si>
-  <si>
-    <t>ムーディ手がかりライト</t>
-  </si>
-  <si>
-    <t>Moody Clue-Lit Frame</t>
-  </si>
-  <si>
-    <t>灰彩調查草稿/グレーウォッシュ捜査スケッチ/Grey Wash Investigation Draft</t>
+    <t>文學小說_ 讀書會小說_氛圍線索光影</t>
+  </si>
+  <si>
+    <t>文学小説_ ブッククラブ小説_ 雰囲気の手がかりと光と影</t>
+  </si>
+  <si>
+    <t>Literary Fiction_ Book Club Fiction_ Clues to Atmosphere, Light and Shadow</t>
+  </si>
+  <si>
+    <t>日常系戀愛喜劇_灰彩調查草稿/日常のロマンティックコメディ - グレースケール調査草稿/Everyday Romantic Comedy - Grayscale Research Draft</t>
   </si>
   <si>
     <t>monochrome grey wash, fine ink lines, selective hatching, low saturation, simple background, quiet detail, high readability, highres</t>
@@ -663,19 +579,16 @@
     <t>A grey-wash investigation-draft treatment with fine ink lines, selective hatching, low saturation, and simple backgrounds for restrained interior mystery illustrations.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 日常系戀愛喜劇</t>
-  </si>
-  <si>
-    <t>灰彩調查草稿</t>
-  </si>
-  <si>
-    <t>グレーウォッシュ捜査スケッチ</t>
-  </si>
-  <si>
-    <t>Grey Wash Investigation Draft</t>
-  </si>
-  <si>
-    <t>暖光工房質感/暖光工房グロウ/Warm Craft Workshop Glow</t>
+    <t>日常系戀愛喜劇_灰彩調查草稿</t>
+  </si>
+  <si>
+    <t>日常のロマンティックコメディ - グレースケール調査草稿</t>
+  </si>
+  <si>
+    <t>Everyday Romantic Comedy - Grayscale Research Draft</t>
+  </si>
+  <si>
+    <t>古典劍與魔法奇幻_暖光工房質感/古典的な剣と魔法のファンタジー - Warm Light Studio テクスチャ/Classic sword and magic fantasy - Warm Light Studio textures</t>
   </si>
   <si>
     <t>warm ambient glow, polished rendering, soft specular highlights, rich material texture, cozy workshop atmosphere, clean lineart, earthy palette, detailed finish, highres</t>
@@ -684,19 +597,16 @@
     <t>A warm craft-workshop treatment with ambient glow, rich material textures, soft specular highlights, earthy tones, and clean detailed lineart for a cozy, artisanal cover.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 古典劍與魔法奇幻</t>
-  </si>
-  <si>
-    <t>暖光工房質感</t>
-  </si>
-  <si>
-    <t>暖光工房グロウ</t>
-  </si>
-  <si>
-    <t>Warm Craft Workshop Glow</t>
-  </si>
-  <si>
-    <t>柔和道具材質習作/柔らか道具素材スケッチ/Soft Tool and Material Study</t>
+    <t>古典劍與魔法奇幻_暖光工房質感</t>
+  </si>
+  <si>
+    <t>古典的な剣と魔法のファンタジー - Warm Light Studio テクスチャ</t>
+  </si>
+  <si>
+    <t>Classic sword and magic fantasy - Warm Light Studio textures</t>
+  </si>
+  <si>
+    <t>史詩太空歌劇_柔和道具材質習作/壮大なスペースオペラ - ソフトプロップ素材の実習/An epic space opera - A soft prop material workshop</t>
   </si>
   <si>
     <t>soft pencil rendering, light watercolor accents, visible material texture, muted earthy palette, low contrast, simple composition, high readability, highres</t>
@@ -705,19 +615,16 @@
     <t>A soft tool-and-material study treatment with pencil rendering, light watercolor accents, visible textures, muted earthy tones, and low contrast for calm interior craft-life illustrations.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 史詩太空歌劇</t>
-  </si>
-  <si>
-    <t>柔和道具材質習作</t>
-  </si>
-  <si>
-    <t>柔らか道具素材スケッチ</t>
-  </si>
-  <si>
-    <t>Soft Tool and Material Study</t>
-  </si>
-  <si>
-    <t>霓虹介面全像/ネオンインターフェースホログラム/Neon Interface Holographic</t>
+    <t>史詩太空歌劇_柔和道具材質習作</t>
+  </si>
+  <si>
+    <t>壮大なスペースオペラ - ソフトプロップ素材の実習</t>
+  </si>
+  <si>
+    <t>An epic space opera - A soft prop material workshop</t>
+  </si>
+  <si>
+    <t>史詩奇幻_ 高奇幻_霓虹介面全像/エピックファンタジー_ハイファンタジー_ネオンインターフェースホログラム/Epic Fantasy High Fantasy Neon Interface Hologram</t>
   </si>
   <si>
     <t>glowing holographic elements, neon interface lines, deep dark background, cyan and magenta rim light, digital texture, futuristic UI overlays, high contrast, clean tech aesthetic, highres</t>
@@ -726,19 +633,16 @@
     <t>A neon interface-holographic treatment with glowing UI lines, cyan-magenta rim light, deep dark backgrounds, and clean tech textures for a virtual-world cover.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 史詩奇幻 &gt; 高奇幻</t>
-  </si>
-  <si>
-    <t>霓虹介面全像</t>
-  </si>
-  <si>
-    <t>ネオンインターフェースホログラム</t>
-  </si>
-  <si>
-    <t>Neon Interface Holographic</t>
-  </si>
-  <si>
-    <t>乾淨HUD線框稿/クリーンHUDワイヤーフレーム/Clean HUD and Wireframe Lineart</t>
+    <t>史詩奇幻_ 高奇幻_霓虹介面全像</t>
+  </si>
+  <si>
+    <t>エピックファンタジー_ハイファンタジー_ネオンインターフェースホログラム</t>
+  </si>
+  <si>
+    <t>Epic Fantasy High Fantasy Neon Interface Hologram</t>
+  </si>
+  <si>
+    <t>生物收集冒險_乾淨HUD線框稿/クリーチャーコレクションアドベンチャー - クリーンなHUDワイヤーフレーム/Creature Collection Adventure - Clean HUD Wireframe</t>
   </si>
   <si>
     <t>clean wireframe lineart, faint HUD elements, monochrome base with spot neon, low saturation, simple background, technical readability, highres</t>
@@ -747,19 +651,16 @@
     <t>A clean HUD-and-wireframe lineart treatment with faint interface elements, monochrome base, spot neon accents, low saturation, and technical clarity for interior virtual-world scenes.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 生物收集冒險</t>
-  </si>
-  <si>
-    <t>乾淨HUD線框稿</t>
-  </si>
-  <si>
-    <t>クリーンHUDワイヤーフレーム</t>
-  </si>
-  <si>
-    <t>Clean HUD and Wireframe Lineart</t>
-  </si>
-  <si>
-    <t>華美歷史細密畫/絢爛歴史ミニアチュール/Ornate Historical Miniature</t>
+    <t>生物收集冒險_乾淨HUD線框稿</t>
+  </si>
+  <si>
+    <t>クリーチャーコレクションアドベンチャー - クリーンなHUDワイヤーフレーム</t>
+  </si>
+  <si>
+    <t>Creature Collection Adventure - Clean HUD Wireframe</t>
+  </si>
+  <si>
+    <t>全年齡卡通冒險_華美歷史細密畫/全年齢対象の漫画アドベンチャー - 精緻な歴史的細密画/A manga adventure suitable for all ages - featuring intricate historical illustrations.</t>
   </si>
   <si>
     <t>ornate miniature painting feel, fine gold detailing, muted jewel tones, aged parchment texture, delicate brushwork, courtly atmosphere, soft diffused light, highres</t>
@@ -768,19 +669,16 @@
     <t>An ornate historical-miniature treatment with fine gold detailing, muted jewel tones, aged parchment texture, delicate brushwork, and a soft courtly atmosphere for a palace-mystery cover.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 全年齡卡通冒險</t>
-  </si>
-  <si>
-    <t>華美歷史細密畫</t>
-  </si>
-  <si>
-    <t>絢爛歴史ミニアチュール</t>
-  </si>
-  <si>
-    <t>Ornate Historical Miniature</t>
-  </si>
-  <si>
-    <t>精緻褐彩細節習作/精緻セピア細部スケッチ/Fine Sepia Detail Study</t>
+    <t>全年齡卡通冒險_華美歷史細密畫</t>
+  </si>
+  <si>
+    <t>全年齢対象の漫画アドベンチャー - 精緻な歴史的細密画</t>
+  </si>
+  <si>
+    <t>A manga adventure suitable for all ages - featuring intricate historical illustrations.</t>
+  </si>
+  <si>
+    <t>奇幻懸疑_ 推理_精緻褐彩細節習作/ファンタジー・サスペンス・ミステリー・絶妙なブラウンのディテール研究/Fantasy, suspense, mystery, and exquisite brown detail study</t>
   </si>
   <si>
     <t>sepia fine lineart, delicate hatching, muted tones, parchment texture, low contrast, elegant detail, high readability, highres</t>
@@ -789,19 +687,16 @@
     <t>A fine sepia detail-study treatment with delicate hatching, muted tones, parchment texture, and low contrast for elegant interior palace-mystery illustrations.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 奇幻懸疑 &gt; 推理</t>
-  </si>
-  <si>
-    <t>精緻褐彩細節習作</t>
-  </si>
-  <si>
-    <t>精緻セピア細部スケッチ</t>
-  </si>
-  <si>
-    <t>Fine Sepia Detail Study</t>
-  </si>
-  <si>
-    <t>遼闊環境史詩/広大環境エピック/Vast Environmental Epic</t>
+    <t>奇幻懸疑_ 推理_精緻褐彩細節習作</t>
+  </si>
+  <si>
+    <t>ファンタジー・サスペンス・ミステリー・絶妙なブラウンのディテール研究</t>
+  </si>
+  <si>
+    <t>Fantasy, suspense, mystery, and exquisite brown detail study</t>
+  </si>
+  <si>
+    <t>東方異世界史詩_遼闊環境史詩/東洋のファンタジー叙事詩 ― 広大な環境叙事詩/An Oriental fantasy epic – a vast environmental epic</t>
   </si>
   <si>
     <t>dramatic landscape, massive scale, lone armored figure, map-like elements, deep blue and purple palette, gold accent, atmospheric perspective, dramatic sky, painterly rendering, high contrast</t>
@@ -810,19 +705,16 @@
     <t>A vast environmental epic treatment with massive scale, a lone armored figure against a dramatic sky, deep blue-purple and gold palette, map-like undertones, atmospheric perspective, and painterly rendering for an epic fantasy cover.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 東方異世界史詩</t>
-  </si>
-  <si>
-    <t>遼闊環境史詩</t>
-  </si>
-  <si>
-    <t>広大環境エピック</t>
-  </si>
-  <si>
-    <t>Vast Environmental Epic</t>
-  </si>
-  <si>
-    <t>古典地圖線稿/古典地図線画/Classical Map and Linework</t>
+    <t>東方異世界史詩_遼闊環境史詩</t>
+  </si>
+  <si>
+    <t>東洋のファンタジー叙事詩 ― 広大な環境叙事詩</t>
+  </si>
+  <si>
+    <t>An Oriental fantasy epic – a vast environmental epic</t>
+  </si>
+  <si>
+    <t>空靈奇幻角色扮演_古典地圖線稿/幻想的なファンタジーロールプレイング_クラシックマップ線画/Fantastical fantasy role-playing game_classic map line art</t>
   </si>
   <si>
     <t>monochrome lineart, map elements, fine hatching, parchment texture, muted earth tones, low contrast, elegant restraint, high readability</t>
@@ -831,19 +723,16 @@
     <t>A classical map-and-linework treatment with monochrome ink, parchment texture, muted earth tones, fine hatching, and low contrast for restrained interior epic-fantasy illustrations.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 空靈奇幻角色扮演</t>
-  </si>
-  <si>
-    <t>古典地圖線稿</t>
-  </si>
-  <si>
-    <t>古典地図線画</t>
-  </si>
-  <si>
-    <t>Classical Map and Linework</t>
-  </si>
-  <si>
-    <t>霓虹都市雙重性/ネオン都市デュアル/Neon Urban Duality</t>
+    <t>空靈奇幻角色扮演_古典地圖線稿</t>
+  </si>
+  <si>
+    <t>幻想的なファンタジーロールプレイング_クラシックマップ線画</t>
+  </si>
+  <si>
+    <t>Fantastical fantasy role-playing game_classic map line art</t>
+  </si>
+  <si>
+    <t>科幻_ 推想小說_霓虹都市雙重性/SF_スペキュラティブ・フィクション_ネオンシティの二重性/SF_Speculative Fiction_The Duality of Neon City</t>
   </si>
   <si>
     <t>crisp linework, high-saturation palette, urban geometry, neon signage, single female figure, magical overlay, contemporary cityscape, stylized realism, dynamic contrast</t>
@@ -852,19 +741,16 @@
     <t>A neon urban-duality treatment with crisp linework, high-saturation neon tones, contemporary urban geometry, a single female figure, and a subtle magical overlay that bridges the everyday and the otherworldly for an urban fantasy cover.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 科幻 &gt; 推想小說</t>
-  </si>
-  <si>
-    <t>霓虹都市雙重性</t>
-  </si>
-  <si>
-    <t>ネオン都市デュアル</t>
-  </si>
-  <si>
-    <t>Neon Urban Duality</t>
-  </si>
-  <si>
-    <t>灰調城市線稿局部色調/グレー都市線画スポットトーン/Grey City Line and Spot Tone</t>
+    <t>科幻_ 推想小說_霓虹都市雙重性</t>
+  </si>
+  <si>
+    <t>SF_スペキュラティブ・フィクション_ネオンシティの二重性</t>
+  </si>
+  <si>
+    <t>SF_Speculative Fiction_The Duality of Neon City</t>
+  </si>
+  <si>
+    <t>英雄奇幻冒險_灰調城市線稿局部色調/英雄的なファンタジーアドベンチャー - グレーがかった都市の線画（部分的な色調）/Heroic fantasy adventure - line drawing of a gray city (with partial coloring)</t>
   </si>
   <si>
     <t>grey lineart, urban texture, spot neon accents, monochrome base, low saturation, simple background, high readability, quiet detail</t>
@@ -873,19 +759,16 @@
     <t>A grey city-line-and-spot-tone treatment with urban textures, monochrome lineart, selective neon accents, low saturation, and simple backgrounds for readable interior urban-fantasy illustrations.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 英雄奇幻冒險</t>
-  </si>
-  <si>
-    <t>灰調城市線稿局部色調</t>
-  </si>
-  <si>
-    <t>グレー都市線画スポットトーン</t>
-  </si>
-  <si>
-    <t>Grey City Line and Spot Tone</t>
-  </si>
-  <si>
-    <t>暗黑巴洛克浪漫奇幻/ダークバロックロマンファンタジー/Dark Baroque Romantic Fantasy</t>
+    <t>英雄奇幻冒險_灰調城市線稿局部色調</t>
+  </si>
+  <si>
+    <t>英雄的なファンタジーアドベンチャー - グレーがかった都市の線画（部分的な色調）</t>
+  </si>
+  <si>
+    <t>Heroic fantasy adventure - line drawing of a gray city (with partial coloring)</t>
+  </si>
+  <si>
+    <t>宮廷謎案_ 歷史戀愛_暗黑巴洛克浪漫奇幻/宮廷ミステリー_歴史ロマンス_ダークバロックロマンティックファンタジー/Court Mystery_Historical Romance_Dark Baroque Romantic Fantasy</t>
   </si>
   <si>
     <t>dark baroque atmosphere, harsh shadow lighting, metallic gold and silver accents, ornate details, intimate composition, fantasy and romance motifs, rich jewel tones, dramatic chiaroscuro</t>
@@ -894,19 +777,16 @@
     <t>A dark baroque romantic-fantasy treatment with harsh shadow lighting, metallic gold-silver inclusions, ornate details, rich jewel tones, and an intimate composition that blends fantasy and romance visual signals for a romantasy cover.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 宮廷謎案 &gt; 歷史戀愛</t>
-  </si>
-  <si>
-    <t>暗黑巴洛克浪漫奇幻</t>
-  </si>
-  <si>
-    <t>ダークバロックロマンファンタジー</t>
-  </si>
-  <si>
-    <t>Dark Baroque Romantic Fantasy</t>
-  </si>
-  <si>
-    <t>裝飾親密細節/装飾的親密ディテール/Ornamental Intimate Detail</t>
+    <t>宮廷謎案_ 歷史戀愛_暗黑巴洛克浪漫奇幻</t>
+  </si>
+  <si>
+    <t>宮廷ミステリー_歴史ロマンス_ダークバロックロマンティックファンタジー</t>
+  </si>
+  <si>
+    <t>Court Mystery_Historical Romance_Dark Baroque Romantic Fantasy</t>
+  </si>
+  <si>
+    <t>恐怖_ 哥德_裝飾親密細節/ホラー_ゴシック_親密な装飾の詳細/Details of horror, gothic, and intimate decor.</t>
   </si>
   <si>
     <t>ornamental detail, fine metallic linework, muted jewel tones, soft chiaroscuro, intimate cropping, delicate texture, low contrast, elegant restraint</t>
@@ -915,19 +795,16 @@
     <t>A restrained ornamental-intimate-detail treatment with fine metallic linework, muted jewel tones, soft chiaroscuro, delicate texture, and low contrast for elegant interior romantasy illustrations.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 恐怖 &gt; 哥德</t>
-  </si>
-  <si>
-    <t>裝飾親密細節</t>
-  </si>
-  <si>
-    <t>装飾的親密ディテール</t>
-  </si>
-  <si>
-    <t>Ornamental Intimate Detail</t>
-  </si>
-  <si>
-    <t>低彩威脅極簡/低彩脅威ミニマル/Muted Menace Minimal</t>
+    <t>恐怖_ 哥德_裝飾親密細節</t>
+  </si>
+  <si>
+    <t>ホラー_ゴシック_親密な装飾の詳細</t>
+  </si>
+  <si>
+    <t>Details of horror, gothic, and intimate decor.</t>
+  </si>
+  <si>
+    <t>校園黨爭_ 群像劇_低彩威脅極簡/キャンパス内の派閥争い_群像劇_低彩度の脅威ミニマリズム/Campus Factional Infighting - Ensemble Drama - The Threat of Low Saturation - Minimalism</t>
   </si>
   <si>
     <t>muted palette, high contrast, single central object, dark mood, limited color scheme, black white and red accents, dramatic shadow, clean typography-ready composition</t>
@@ -936,19 +813,16 @@
     <t>A muted-menace minimal treatment with a restrained palette, high contrast, a single dominant object or silhouette, dark mood, and a limited black-white-red accent scheme for a thriller or suspense cover that signals danger instantly.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 校園黨爭 &gt; 群像劇</t>
-  </si>
-  <si>
-    <t>低彩威脅極簡</t>
-  </si>
-  <si>
-    <t>低彩脅威ミニマル</t>
-  </si>
-  <si>
-    <t>Muted Menace Minimal</t>
-  </si>
-  <si>
-    <t>黑色調查淡染/ノワール淡彩捜査/Noir Wash Investigation</t>
+    <t>校園黨爭_ 群像劇_低彩威脅極簡</t>
+  </si>
+  <si>
+    <t>キャンパス内の派閥争い_群像劇_低彩度の脅威ミニマリズム</t>
+  </si>
+  <si>
+    <t>Campus Factional Infighting - Ensemble Drama - The Threat of Low Saturation - Minimalism</t>
+  </si>
+  <si>
+    <t>浪漫小說_ 當代浪漫_黑色調查淡染/ロマンス小説_現代ロマンス_ダークな調査（希釈版）/Romance Novel_Modern Romance_Dark Investigation (Diluted Version)</t>
   </si>
   <si>
     <t>noir ink wash, monochrome grey, selective hatching, deep shadow, low saturation, simple geometry, quiet detail, high readability</t>
@@ -957,19 +831,16 @@
     <t>A noir ink-wash investigation treatment with monochrome grey tones, selective hatching, deep shadow blocks, low saturation, and quiet detail for restrained interior thriller illustrations.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 浪漫小說 &gt; 當代浪漫</t>
-  </si>
-  <si>
-    <t>黑色調查淡染</t>
-  </si>
-  <si>
-    <t>ノワール淡彩捜査</t>
-  </si>
-  <si>
-    <t>Noir Wash Investigation</t>
-  </si>
-  <si>
-    <t>暗色浪漫氛圍/ダークロマンチック雰囲気/Dark Romantic Atmosphere</t>
+    <t>浪漫小說_ 當代浪漫_黑色調查淡染</t>
+  </si>
+  <si>
+    <t>ロマンス小説_現代ロマンス_ダークな調査（希釈版）</t>
+  </si>
+  <si>
+    <t>Romance Novel_Modern Romance_Dark Investigation (Diluted Version)</t>
+  </si>
+  <si>
+    <t>浪漫奇幻_ 浪漫小說_暗色浪漫氛圍/ロマンティックファンタジー_ロマンティック小説_ダークロマンティックな雰囲気/Romantic fantasy, romantic novel, dark romantic atmosphere</t>
   </si>
   <si>
     <t>deep shadow, moody chiaroscuro, single attractive figure, dramatic directional light, rich dark palette, metallic title-ready negative space, elegant tension</t>
@@ -978,19 +849,16 @@
     <t>A dark romantic-atmosphere treatment with deep shadow, moody chiaroscuro, a single central figure, dramatic directional light, and rich dark tones for a romance or dark-romance cover that prioritizes tension and desirability.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 浪漫奇幻 &gt; 浪漫小說</t>
-  </si>
-  <si>
-    <t>暗色浪漫氛圍</t>
-  </si>
-  <si>
-    <t>ダークロマンチック雰囲気</t>
-  </si>
-  <si>
-    <t>Dark Romantic Atmosphere</t>
-  </si>
-  <si>
-    <t>柔焦親密素描/ソフトフォーカス親密スケッチ/Soft Focus Intimate Sketch</t>
+    <t>浪漫奇幻_ 浪漫小說_暗色浪漫氛圍</t>
+  </si>
+  <si>
+    <t>ロマンティックファンタジー_ロマンティック小説_ダークロマンティックな雰囲気</t>
+  </si>
+  <si>
+    <t>Romantic fantasy, romantic novel, dark romantic atmosphere</t>
+  </si>
+  <si>
+    <t>現代都市奇幻_柔焦親密素描/現代都市ファンタジー - ソフトフォーカスによる親密なスケッチ/Modern urban fantasy - Intimate sketches with soft focus</t>
   </si>
   <si>
     <t>soft pencil sketch, light tonal shading, intimate close-up feel, muted warm palette, gentle contrast, delicate detail, paper texture</t>
@@ -999,19 +867,16 @@
     <t>A soft-focus intimate-sketch treatment with pencil rendering, light tonal shading, muted warm tones, delicate detail, and paper texture for gentle interior romance illustrations.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 現代都市奇幻</t>
-  </si>
-  <si>
-    <t>柔焦親密素描</t>
-  </si>
-  <si>
-    <t>ソフトフォーカス親密スケッチ</t>
-  </si>
-  <si>
-    <t>Soft Focus Intimate Sketch</t>
-  </si>
-  <si>
-    <t>溫暖插畫舒適/温かいイラストコージー/Warm Illustrated Cozy</t>
+    <t>現代都市奇幻_柔焦親密素描</t>
+  </si>
+  <si>
+    <t>現代都市ファンタジー - ソフトフォーカスによる親密なスケッチ</t>
+  </si>
+  <si>
+    <t>Modern urban fantasy - Intimate sketches with soft focus</t>
+  </si>
+  <si>
+    <t>都市奇幻_溫暖插畫舒適/アーバンファンタジー_温かく心地よいイラスト/Urban Fantasy - Warm and Comforting Illustrations</t>
   </si>
   <si>
     <t>warm illustrated style, soft rounded shapes, cozy palette, approachable characters, whimsical detail, cottagecore influence, gentle lighting, inviting atmosphere</t>
@@ -1020,19 +885,16 @@
     <t>A warm illustrated cozy treatment with soft rounded shapes, a cozy warm palette, approachable figures, whimsical cottagecore-influenced detail, and gentle inviting lighting for a cozy fantasy cover.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 都市奇幻</t>
-  </si>
-  <si>
-    <t>溫暖插畫舒適</t>
-  </si>
-  <si>
-    <t>温かいイラストコージー</t>
-  </si>
-  <si>
-    <t>Warm Illustrated Cozy</t>
-  </si>
-  <si>
-    <t>柔彩鉛筆細節/柔らか色鉛筆ディテール/Soft Colored Pencil Detail</t>
+    <t>都市奇幻_溫暖插畫舒適</t>
+  </si>
+  <si>
+    <t>アーバンファンタジー_温かく心地よいイラスト</t>
+  </si>
+  <si>
+    <t>Urban Fantasy - Warm and Comforting Illustrations</t>
+  </si>
+  <si>
+    <t>舒適奇幻_ 溫馨奇幻_柔彩鉛筆細節/心地よいファンタジー_ 温かいファンタジー_ 柔らかな色鉛筆の詳細/A comforting fantasy_ A warm fantasy_ Details of soft colored pencils</t>
   </si>
   <si>
     <t>soft colored pencil rendering, warm muted palette, gentle linework, simple domestic detail, low contrast, inviting texture, high readability</t>
@@ -1041,19 +903,16 @@
     <t>A soft colored-pencil-detail treatment with warm muted tones, gentle linework, simple domestic textures, low contrast, and inviting readability for cozy interior fantasy illustrations.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 舒適奇幻 &gt; 溫馨奇幻</t>
-  </si>
-  <si>
-    <t>柔彩鉛筆細節</t>
-  </si>
-  <si>
-    <t>柔らか色鉛筆ディテール</t>
-  </si>
-  <si>
-    <t>Soft Colored Pencil Detail</t>
-  </si>
-  <si>
-    <t>電影感推想框架/シネマティック思弁フレーム/Cinematic Speculative Frame</t>
+    <t>舒適奇幻_ 溫馨奇幻_柔彩鉛筆細節</t>
+  </si>
+  <si>
+    <t>心地よいファンタジー_ 温かいファンタジー_ 柔らかな色鉛筆の詳細</t>
+  </si>
+  <si>
+    <t>A comforting fantasy_ A warm fantasy_ Details of soft colored pencils</t>
+  </si>
+  <si>
+    <t>慢生活_ 職人奇幻_電影感推想框架/スローリビング_職人ファンタジー_映画的含意フレームワーク/Slow Living - Craftsman Fantasy - Cinematic Implications Framework</t>
   </si>
   <si>
     <t>cinematic composition, high-concept visual, cool and sterile palette, sharp focal contrast, subtle atmospheric haze, futuristic or speculative elements, dramatic scale, polished rendering</t>
@@ -1062,19 +921,16 @@
     <t>A cinematic speculative-frame treatment with high-concept visual clarity, a cool restrained palette, sharp focal contrast, subtle atmospheric haze, and dramatic scale for a science-fiction or speculative cover.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 慢生活 &gt; 職人奇幻</t>
-  </si>
-  <si>
-    <t>電影感推想框架</t>
-  </si>
-  <si>
-    <t>シネマティック思弁フレーム</t>
-  </si>
-  <si>
-    <t>Cinematic Speculative Frame</t>
-  </si>
-  <si>
-    <t>技術氛圍線稿/テクニカル雰囲気線画/Technical Atmosphere Lineart</t>
+    <t>慢生活_ 職人奇幻_電影感推想框架</t>
+  </si>
+  <si>
+    <t>スローリビング_職人ファンタジー_映画的含意フレームワーク</t>
+  </si>
+  <si>
+    <t>Slow Living - Craftsman Fantasy - Cinematic Implications Framework</t>
+  </si>
+  <si>
+    <t>機甲心理劇_技術氛圍線稿/メカサイコドラマ - テクニカルな雰囲気の線画/Mecha-Psychodrama - Line drawings with a technical feel</t>
   </si>
   <si>
     <t>technical lineart, monochrome with cool accent, fine structural detail, low saturation, atmospheric negative space, clean diagram feel, high readability</t>
@@ -1083,19 +939,16 @@
     <t>A technical-atmosphere lineart treatment with fine structural detail, monochrome base, cool accent tones, low saturation, and clean diagram-like clarity for interior science-fiction illustrations.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 機甲心理劇</t>
-  </si>
-  <si>
-    <t>技術氛圍線稿</t>
-  </si>
-  <si>
-    <t>テクニカル雰囲気線画</t>
-  </si>
-  <si>
-    <t>Technical Atmosphere Lineart</t>
-  </si>
-  <si>
-    <t>哥德恐懼質感/ゴシックドレッドテクスチャ/Gothic Dread Texture</t>
+    <t>機甲心理劇_技術氛圍線稿</t>
+  </si>
+  <si>
+    <t>メカサイコドラマ - テクニカルな雰囲気の線画</t>
+  </si>
+  <si>
+    <t>Mecha-Psychodrama - Line drawings with a technical feel</t>
+  </si>
+  <si>
+    <t>賽博龐克科技黑色_哥德恐懼質感/サイバーパンク テック ブラック_ゴシック ホラー テクスチャ/Cyberpunk Tech Black Gothic Horror Textures</t>
   </si>
   <si>
     <t>desaturated palette, gothic texture, fragmented shadow, rough brush energy, limited red and black, ominous negative space, distressed surface, atmospheric unease</t>
@@ -1104,19 +957,16 @@
     <t>A gothic dread-texture treatment with a desaturated palette, fragmented shadows, rough brush energy, a limited red-black scheme, distressed surface textures, and ominous negative space for a horror or gothic cover.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 賽博龐克科技黑色</t>
-  </si>
-  <si>
-    <t>哥德恐懼質感</t>
-  </si>
-  <si>
-    <t>ゴシックドレッドテクスチャ</t>
-  </si>
-  <si>
-    <t>Gothic Dread Texture</t>
-  </si>
-  <si>
-    <t>粗炭不安/粗い炭の不安/Rough Charcoal Unease</t>
+    <t>賽博龐克科技黑色_哥德恐懼質感</t>
+  </si>
+  <si>
+    <t>サイバーパンク テック ブラック_ゴシック ホラー テクスチャ</t>
+  </si>
+  <si>
+    <t>Cyberpunk Tech Black Gothic Horror Textures</t>
+  </si>
+  <si>
+    <t>轉生惡役千金_ 宮廷戀愛_粗炭不安/悪役令嬢に転生したらロイヤルロマンス - ラフチャコールとアンイージー/Reincarnated as a Villainess: A Royal Romance - Rough Charcoal and Uneasy</t>
   </si>
   <si>
     <t>rough charcoal sketch, heavy grain, uneven dark strokes, low brightness, simple ominous forms, high contrast pockets, unsettling negative space</t>
@@ -1125,19 +975,16 @@
     <t>A rough charcoal-unease treatment with heavy grain, uneven dark strokes, low brightness, simple ominous forms, and high-contrast shadow pockets for interior horror illustrations.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 轉生惡役千金 &gt; 宮廷戀愛</t>
-  </si>
-  <si>
-    <t>粗炭不安</t>
-  </si>
-  <si>
-    <t>粗い炭の不安</t>
-  </si>
-  <si>
-    <t>Rough Charcoal Unease</t>
-  </si>
-  <si>
-    <t>文學節制框架/文学抑制フレーム/Literary Restraint Frame</t>
+    <t>轉生惡役千金_ 宮廷戀愛_粗炭不安</t>
+  </si>
+  <si>
+    <t>悪役令嬢に転生したらロイヤルロマンス - ラフチャコールとアンイージー</t>
+  </si>
+  <si>
+    <t>Reincarnated as a Villainess: A Royal Romance - Rough Charcoal and Uneasy</t>
+  </si>
+  <si>
+    <t>驚悚_ 懸疑_ 犯罪_文學節制框架/スリラー・ミステリー・犯罪・文学的制約フレームワーク/Thriller, Mystery, Crime, Literary Constraints Framework</t>
   </si>
   <si>
     <t>understated composition, literary restraint, muted sophisticated palette, symbolic single element, generous negative space, fine texture, quiet atmospheric light, subtle tension</t>
@@ -1146,19 +993,16 @@
     <t>A literary-restraint frame treatment with understated composition, a muted sophisticated palette, a single symbolic element, generous negative space, and quiet atmospheric light for upmarket literary or book-club fiction covers.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; 驚悚 &gt; 懸疑 &gt; 犯罪</t>
-  </si>
-  <si>
-    <t>文學節制框架</t>
-  </si>
-  <si>
-    <t>文学抑制フレーム</t>
-  </si>
-  <si>
-    <t>Literary Restraint Frame</t>
-  </si>
-  <si>
-    <t>精緻象徵淡彩/繊細象徴淡彩/Delicate Symbolic Wash</t>
+    <t>驚悚_ 懸疑_ 犯罪_文學節制框架</t>
+  </si>
+  <si>
+    <t>スリラー・ミステリー・犯罪・文学的制約フレームワーク</t>
+  </si>
+  <si>
+    <t>Thriller, Mystery, Crime, Literary Constraints Framework</t>
+  </si>
+  <si>
+    <t>VR遊戲_ 虛擬世界_精緻象徵淡彩/VRゲーム_仮想世界_絶妙な象徴的な淡い色彩/VR Games - Virtual Worlds - Exquisite, Symbolic, and Subtle Colors</t>
   </si>
   <si>
     <t>delicate watercolor wash, pale symbolic motif, fine paper grain, low contrast, muted sophisticated tone, generous white space, restrained detail</t>
@@ -1167,16 +1011,556 @@
     <t>A delicate symbolic-wash treatment with pale watercolor, a restrained symbolic motif, fine paper grain, low contrast, muted tones, and generous white space for interior literary illustrations.</t>
   </si>
   <si>
-    <t>封面藝術風格,封面藝術風格 &gt; VR遊戲 &gt; 虛擬世界</t>
-  </si>
-  <si>
-    <t>精緻象徵淡彩</t>
-  </si>
-  <si>
-    <t>繊細象徴淡彩</t>
-  </si>
-  <si>
-    <t>Delicate Symbolic Wash</t>
+    <t>VR遊戲_ 虛擬世界_精緻象徵淡彩</t>
+  </si>
+  <si>
+    <t>VRゲーム_仮想世界_絶妙な象徴的な淡い色彩</t>
+  </si>
+  <si>
+    <t>VR Games - Virtual Worlds - Exquisite, Symbolic, and Subtle Colors</t>
+  </si>
+  <si>
+    <t>唯美主義/美学/Aestheticism</t>
+  </si>
+  <si>
+    <t>aestheticism style, art for art's sake, formal beauty, sensory pleasure, peacock motifs, refined tonal harmony</t>
+  </si>
+  <si>
+    <t>A refined visual language that prioritizes pure formal beauty and sensory pleasure above narrative or moral content, often featuring peacock motifs and harmonious tonal arrangements.</t>
+  </si>
+  <si>
+    <t>藝術形式</t>
+  </si>
+  <si>
+    <t>唯美主義</t>
+  </si>
+  <si>
+    <t>美学</t>
+  </si>
+  <si>
+    <t>Aestheticism</t>
+  </si>
+  <si>
+    <t>矯飾主義/マニエリスム/Mannerism</t>
+  </si>
+  <si>
+    <t>mannerism style, elongated figures, complex composition, formal tension, elegant distortion</t>
+  </si>
+  <si>
+    <t>An elegant yet tense style defined by elongated proportions, intricate spatial arrangements, and deliberate formal distortion that creates sophisticated visual tension.</t>
+  </si>
+  <si>
+    <t>矯飾主義</t>
+  </si>
+  <si>
+    <t>マニエリスム</t>
+  </si>
+  <si>
+    <t>Mannerism</t>
+  </si>
+  <si>
+    <t>未來主義/未来主義/Futurism</t>
+  </si>
+  <si>
+    <t>futurism style, speed worship, overlapping motion, mechanical rhythm, dynamic energy</t>
+  </si>
+  <si>
+    <t>A dynamic celebration of speed, mechanical energy, and modern life expressed through overlapping forms, rhythmic lines, and a sense of continuous motion.</t>
+  </si>
+  <si>
+    <t>未來主義</t>
+  </si>
+  <si>
+    <t>未来主義</t>
+  </si>
+  <si>
+    <t>Futurism</t>
+  </si>
+  <si>
+    <t>奧爾菲主義/オルフェウス教/Orphism</t>
+  </si>
+  <si>
+    <t>orphism style, pure color autonomy, simultaneous contrast, rhythmic composition, luminous abstraction</t>
+  </si>
+  <si>
+    <t>An abstract approach centered on the independent power of pure color, simultaneous contrasts, and rhythmic luminous compositions that evoke musical harmony.</t>
+  </si>
+  <si>
+    <t>奧爾菲主義</t>
+  </si>
+  <si>
+    <t>オルフェウス教</t>
+  </si>
+  <si>
+    <t>Orphism</t>
+  </si>
+  <si>
+    <t>渦旋/渦運動/Vorticism</t>
+  </si>
+  <si>
+    <t>vorticism style, mechanical imagery, geometric tension, frozen dynamism, angular abstraction</t>
+  </si>
+  <si>
+    <t>A sharp angular style that fuses machine imagery with geometric tension, capturing modern industrial energy in a state of concentrated, almost crystalline dynamism.</t>
+  </si>
+  <si>
+    <t>渦旋</t>
+  </si>
+  <si>
+    <t>渦運動</t>
+  </si>
+  <si>
+    <t>Vorticism</t>
+  </si>
+  <si>
+    <t>德國表現主義/ドイツ表現主義/German Expressionism</t>
+  </si>
+  <si>
+    <t>german expressionism style, emotional externalization, distorted forms, strong contrast, intense color</t>
+  </si>
+  <si>
+    <t>An intense emotional style that externalizes inner feeling through distorted forms, violent color contrasts, and raw expressive distortion of the visible world.</t>
+  </si>
+  <si>
+    <t>德國表現主義</t>
+  </si>
+  <si>
+    <t>ドイツ表現主義</t>
+  </si>
+  <si>
+    <t>German Expressionism</t>
+  </si>
+  <si>
+    <t>象徵意義/象徴主義/Symbolism</t>
+  </si>
+  <si>
+    <t>symbolism style, inner imagery, symbolic suggestion, dream association, mysterious atmosphere</t>
+  </si>
+  <si>
+    <t>A mysterious style that suggests inner states and dreamlike associations through symbolic imagery rather than direct representation of external reality.</t>
+  </si>
+  <si>
+    <t>象徵意義</t>
+  </si>
+  <si>
+    <t>象徴主義</t>
+  </si>
+  <si>
+    <t>Symbolism</t>
+  </si>
+  <si>
+    <t>社會現實主義/社会リアリズム/Social Realism</t>
+  </si>
+  <si>
+    <t>social realism style, social concern, everyday life of people, realistic critique, muted tones</t>
+  </si>
+  <si>
+    <t>A grounded approach focused on social conditions and ordinary lives, rendered with clear observational realism and a critical yet restrained tone.</t>
+  </si>
+  <si>
+    <t>社會現實主義</t>
+  </si>
+  <si>
+    <t>社会リアリズム</t>
+  </si>
+  <si>
+    <t>Social Realism</t>
+  </si>
+  <si>
+    <t>新印象主義/新印象派/Neo-Impressionism</t>
+  </si>
+  <si>
+    <t>neo-impressionism style, color division, optical mixing, ordered composition, pointillist dots</t>
+  </si>
+  <si>
+    <t>A systematic method of applying pure divided color in ordered dots so that optical mixing produces luminous effects under a carefully structured composition.</t>
+  </si>
+  <si>
+    <t>新印象主義</t>
+  </si>
+  <si>
+    <t>新印象派</t>
+  </si>
+  <si>
+    <t>Neo-Impressionism</t>
+  </si>
+  <si>
+    <t>美國區域主義/アメリカの地域主義/American Regionalism</t>
+  </si>
+  <si>
+    <t>american regionalism style, rural subject, regional narrative, figurative expression, countryside</t>
+  </si>
+  <si>
+    <t>A figurative style devoted to specific American regions, emphasizing rural subjects, local narrative, and a clear, accessible representation of place.</t>
+  </si>
+  <si>
+    <t>美國區域主義</t>
+  </si>
+  <si>
+    <t>アメリカの地域主義</t>
+  </si>
+  <si>
+    <t>American Regionalism</t>
+  </si>
+  <si>
+    <t>現實主義/リアリズム/Realism</t>
+  </si>
+  <si>
+    <t>realism style, everyday subject, plain expression, social observation, natural light</t>
+  </si>
+  <si>
+    <t>A straightforward approach that observes everyday subjects and social conditions with plain, unidealized expression under natural light.</t>
+  </si>
+  <si>
+    <t>現實主義</t>
+  </si>
+  <si>
+    <t>リアリズム</t>
+  </si>
+  <si>
+    <t>Realism</t>
+  </si>
+  <si>
+    <t>照片寫實主義/フォトリアリズム/Photorealism</t>
+  </si>
+  <si>
+    <t>photorealism style, photographic language, precise depiction, detail reproduction, urban reflection</t>
+  </si>
+  <si>
+    <t>A highly precise style that adopts photographic language to reproduce surfaces, reflections, and minute details with meticulous fidelity.</t>
+  </si>
+  <si>
+    <t>照片寫實主義</t>
+  </si>
+  <si>
+    <t>フォトリアリズム</t>
+  </si>
+  <si>
+    <t>Photorealism</t>
+  </si>
+  <si>
+    <t>新藝術運動/アール・ヌーヴォー/Art Nouveau</t>
+  </si>
+  <si>
+    <t>art nouveau style, natural curves, organic forms, total design, flowing lines</t>
+  </si>
+  <si>
+    <t>A decorative style based on flowing natural curves and organic forms that seeks a complete unified design across every element.</t>
+  </si>
+  <si>
+    <t>新藝術運動</t>
+  </si>
+  <si>
+    <t>アール・ヌーヴォー</t>
+  </si>
+  <si>
+    <t>Art Nouveau</t>
+  </si>
+  <si>
+    <t>維也納分離派/ウィーン分離派/Vienna Secession</t>
+  </si>
+  <si>
+    <t>vienna secession style, artistic innovation, total design, decorative exploration, geometric pattern</t>
+  </si>
+  <si>
+    <t>An innovative decorative approach that combines artistic reform with total design principles and exploratory geometric patterning.</t>
+  </si>
+  <si>
+    <t>維也納分離派</t>
+  </si>
+  <si>
+    <t>ウィーン分離派</t>
+  </si>
+  <si>
+    <t>Vienna Secession</t>
+  </si>
+  <si>
+    <t>工藝美術運動/アーツ・アンド・クラフツ運動/Arts and Crafts Movement</t>
+  </si>
+  <si>
+    <t>arts and crafts movement style, handmade value, material honesty, artistic life, tapestry pattern</t>
+  </si>
+  <si>
+    <t>A philosophy of design that values honest materials, handmade quality, and the integration of art into everyday life through patterned craft.</t>
+  </si>
+  <si>
+    <t>工藝美術運動</t>
+  </si>
+  <si>
+    <t>アーツ・アンド・クラフツ運動</t>
+  </si>
+  <si>
+    <t>Arts and Crafts Movement</t>
+  </si>
+  <si>
+    <t>國際歌德式/インターナショナル・ゴシック/International Gothic</t>
+  </si>
+  <si>
+    <t>international gothic style, elegant lines, dense decoration, courtly taste, refined detail</t>
+  </si>
+  <si>
+    <t>A refined courtly style marked by elegant flowing lines, dense ornamental detail, and a sophisticated decorative sensibility.</t>
+  </si>
+  <si>
+    <t>國際歌德式</t>
+  </si>
+  <si>
+    <t>インターナショナル・ゴシック</t>
+  </si>
+  <si>
+    <t>International Gothic</t>
+  </si>
+  <si>
+    <t>文藝復興盛期/盛期ルネサンス/High Renaissance</t>
+  </si>
+  <si>
+    <t>high renaissance style, balanced composition, ideal form, harmonious order, classical architecture</t>
+  </si>
+  <si>
+    <t>A classical ideal of balanced composition, harmonious proportions, and idealized human form arranged in clear spatial order.</t>
+  </si>
+  <si>
+    <t>文藝復興盛期</t>
+  </si>
+  <si>
+    <t>盛期ルネサンス</t>
+  </si>
+  <si>
+    <t>High Renaissance</t>
+  </si>
+  <si>
+    <t>印象主義/印象派/Impressionism</t>
+  </si>
+  <si>
+    <t>impressionism style, momentary light and color, outdoor sketch, lively brushwork, atmospheric effect</t>
+  </si>
+  <si>
+    <t>A direct outdoor approach that captures fleeting effects of light and atmosphere through lively, broken brushwork and pure color.</t>
+  </si>
+  <si>
+    <t>印象主義</t>
+  </si>
+  <si>
+    <t>印象派</t>
+  </si>
+  <si>
+    <t>Impressionism</t>
+  </si>
+  <si>
+    <t>後印象主義/ポスト印象派/Post-Impressionism</t>
+  </si>
+  <si>
+    <t>post-impressionism style, subjective expression, color exploration, formal innovation, structural form</t>
+  </si>
+  <si>
+    <t>A more structured and subjective response to Impressionism that explores personal expression, heightened color, and formal innovation.</t>
+  </si>
+  <si>
+    <t>後印象主義</t>
+  </si>
+  <si>
+    <t>ポスト印象派</t>
+  </si>
+  <si>
+    <t>Post-Impressionism</t>
+  </si>
+  <si>
+    <t>前拉斐爾主義/ラファエル前派/Pre-Raphaelitism</t>
+  </si>
+  <si>
+    <t>pre-raphaelitism style, close observation of nature, literary narrative, symbolic meaning, detailed landscape</t>
+  </si>
+  <si>
+    <t>A detailed and sincere style that returns to close observation of nature combined with literary narrative and layered symbolic meaning.</t>
+  </si>
+  <si>
+    <t>前拉斐爾主義</t>
+  </si>
+  <si>
+    <t>ラファエル前派</t>
+  </si>
+  <si>
+    <t>Pre-Raphaelitism</t>
+  </si>
+  <si>
+    <t>野獸派/フォーヴィスム/Fauvism</t>
+  </si>
+  <si>
+    <t>fauvism style, intense color, subjective coloring, simplified form, bold outline</t>
+  </si>
+  <si>
+    <t>A bold style that liberates color from descriptive duty, using intense subjective hues, simplified forms, and strong outlines.</t>
+  </si>
+  <si>
+    <t>野獸派</t>
+  </si>
+  <si>
+    <t>フォーヴィスム</t>
+  </si>
+  <si>
+    <t>Fauvism</t>
+  </si>
+  <si>
+    <t>納比斯/ナビス/Nabis</t>
+  </si>
+  <si>
+    <t>nabis style, flat color planes, decorative order, subjective synthesis, patterned surface</t>
+  </si>
+  <si>
+    <t>A decorative approach that treats the picture as a flat patterned surface of ordered color planes guided by subjective synthesis.</t>
+  </si>
+  <si>
+    <t>納比斯</t>
+  </si>
+  <si>
+    <t>ナビス</t>
+  </si>
+  <si>
+    <t>Nabis</t>
+  </si>
+  <si>
+    <t>哈林文藝復興/ハーレム・ルネッサンス/Harlem Renaissance</t>
+  </si>
+  <si>
+    <t>harlem renaissance style, african american subject, cultural self-awareness, modern exploration</t>
+  </si>
+  <si>
+    <t>A cultural flowering that asserts African American identity and self-awareness while exploring modern forms of expression.</t>
+  </si>
+  <si>
+    <t>哈林文藝復興</t>
+  </si>
+  <si>
+    <t>ハーレム・ルネッサンス</t>
+  </si>
+  <si>
+    <t>Harlem Renaissance</t>
+  </si>
+  <si>
+    <t>蘇格蘭色彩主義者/スコットランドのカラーリスト/Scottish Colourists</t>
+  </si>
+  <si>
+    <t>scottish colourists style, vivid color, free brushwork, simplified form, coastal light</t>
+  </si>
+  <si>
+    <t>A lively style characterized by vivid color, free brushwork, simplified forms, and a strong response to coastal light.</t>
+  </si>
+  <si>
+    <t>蘇格蘭色彩主義者</t>
+  </si>
+  <si>
+    <t>スコットランドのカラーリスト</t>
+  </si>
+  <si>
+    <t>Scottish Colourists</t>
+  </si>
+  <si>
+    <t>卡姆登鎮集團/カムデン・タウン・グループ/Camden Town Group</t>
+  </si>
+  <si>
+    <t>camden town group style, everyday subject, color exploration, modern viewpoint, urban scene</t>
+  </si>
+  <si>
+    <t>A modern observational style focused on ordinary urban and suburban subjects, explored through heightened color and contemporary viewpoint.</t>
+  </si>
+  <si>
+    <t>卡姆登鎮集團</t>
+  </si>
+  <si>
+    <t>カムデン・タウン・グループ</t>
+  </si>
+  <si>
+    <t>Camden Town Group</t>
+  </si>
+  <si>
+    <t>形而上學繪畫/形而上絵画/Metaphysical Painting</t>
+  </si>
+  <si>
+    <t>metaphysical painting style, silent space, displaced relationships, mysterious atmosphere, empty architecture</t>
+  </si>
+  <si>
+    <t>A silent enigmatic style that places ordinary objects and architecture in strangely displaced relationships, creating a sense of metaphysical mystery.</t>
+  </si>
+  <si>
+    <t>形而上學繪畫</t>
+  </si>
+  <si>
+    <t>形而上絵画</t>
+  </si>
+  <si>
+    <t>Metaphysical Painting</t>
+  </si>
+  <si>
+    <t>純粹主義/純粋主義/Purism</t>
+  </si>
+  <si>
+    <t>purism style, clear form, ordered composition, rational restraint, pure geometry</t>
+  </si>
+  <si>
+    <t>A restrained classical modernism that seeks clear geometric forms, ordered composition, and rational purity of structure.</t>
+  </si>
+  <si>
+    <t>純粹主義</t>
+  </si>
+  <si>
+    <t>純粋主義</t>
+  </si>
+  <si>
+    <t>Purism</t>
+  </si>
+  <si>
+    <t>新客觀主義/新客観主義/New Objectivity</t>
+  </si>
+  <si>
+    <t>new objectivity style, cool observation, clear form, realistic scrutiny, precise outline</t>
+  </si>
+  <si>
+    <t>A cool, clear-eyed style of precise observation that rejects expressionist distortion in favor of sharp realistic scrutiny.</t>
+  </si>
+  <si>
+    <t>新客觀主義</t>
+  </si>
+  <si>
+    <t>新客観主義</t>
+  </si>
+  <si>
+    <t>New Objectivity</t>
+  </si>
+  <si>
+    <t>精確主義/精密主義/Precisionism</t>
+  </si>
+  <si>
+    <t>precisionism style, industrial subject, geometric order, clear outline, machine age</t>
+  </si>
+  <si>
+    <t>A precise geometric style that elevates industrial architecture and machine forms into ordered, clearly outlined compositions.</t>
+  </si>
+  <si>
+    <t>精確主義</t>
+  </si>
+  <si>
+    <t>精密主義</t>
+  </si>
+  <si>
+    <t>Precisionism</t>
+  </si>
+  <si>
+    <t>立體主義/キュービズム/Cubism</t>
+  </si>
+  <si>
+    <t>cubism style, multiple viewpoints, geometric decomposition, spatial reconstruction, fragmented form</t>
+  </si>
+  <si>
+    <t>A radical method that decomposes objects into geometric facets, presents multiple viewpoints simultaneously, and reconstructs space on the flat surface.</t>
+  </si>
+  <si>
+    <t>立體主義</t>
+  </si>
+  <si>
+    <t>キュービズム</t>
+  </si>
+  <si>
+    <t>Cubism</t>
   </si>
 </sst>
 </file>
@@ -1340,8 +1724,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="5" max="5" width="53.8515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -1376,141 +1763,144 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
         <v>43</v>
@@ -1533,1267 +1923,2021 @@
         <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
         <v>49</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>50</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>51</v>
-      </c>
-      <c r="H8" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
         <v>53</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>54</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
         <v>55</v>
       </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>56</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>57</v>
-      </c>
-      <c r="G9" t="s">
-        <v>58</v>
-      </c>
-      <c r="H9" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
         <v>60</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
         <v>61</v>
       </c>
-      <c r="C10" t="s">
+      <c r="G10" t="s">
         <v>62</v>
       </c>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="H10" t="s">
         <v>63</v>
-      </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
         <v>67</v>
       </c>
-      <c r="B11" t="s">
+      <c r="G11" t="s">
         <v>68</v>
       </c>
-      <c r="C11" t="s">
+      <c r="H11" t="s">
         <v>69</v>
-      </c>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" t="s">
-        <v>72</v>
-      </c>
-      <c r="H11" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" t="s">
         <v>74</v>
       </c>
-      <c r="B12" t="s">
+      <c r="H12" t="s">
         <v>75</v>
-      </c>
-      <c r="C12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" t="s">
-        <v>78</v>
-      </c>
-      <c r="G12" t="s">
-        <v>79</v>
-      </c>
-      <c r="H12" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" t="s">
         <v>81</v>
-      </c>
-      <c r="B13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s">
-        <v>84</v>
-      </c>
-      <c r="F13" t="s">
-        <v>85</v>
-      </c>
-      <c r="G13" t="s">
-        <v>86</v>
-      </c>
-      <c r="H13" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="G14" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H14" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G15" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H15" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G16" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H16" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B17" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C17" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>111</v>
+        <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="G17" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="H17" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B18" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>118</v>
+        <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="G18" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="H18" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B19" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
       <c r="F19" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="G19" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="H19" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>132</v>
+        <v>12</v>
       </c>
       <c r="F20" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="G20" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="H20" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B21" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C21" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="G21" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="H21" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="B22" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="C22" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="F22" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="G22" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="H22" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="B23" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C23" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="D23" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>153</v>
+        <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="G23" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="H23" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="B24" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C24" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>160</v>
+        <v>12</v>
       </c>
       <c r="F24" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="G24" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="H24" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="B25" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="C25" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="D25" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>167</v>
+        <v>12</v>
       </c>
       <c r="F25" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="G25" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="H25" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="B26" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="C26" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="D26" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>174</v>
+        <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="G26" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="H26" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="B27" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="C27" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="D27" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>181</v>
+        <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="G27" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="H27" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="B28" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C28" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="D28" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>188</v>
+        <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="G28" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="H28" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="B29" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="C29" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D29" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="F29" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="G29" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="H29" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="B30" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C30" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="D30" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="F30" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="G30" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="H30" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="B31" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="C31" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>209</v>
+        <v>175</v>
       </c>
       <c r="F31" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="G31" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="H31" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="B32" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="C32" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="D32" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E32" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="F32" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="G32" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="H32" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="B33" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="C33" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="D33" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>223</v>
+        <v>175</v>
       </c>
       <c r="F33" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="G33" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="H33" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B34" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="C34" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="D34" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E34" t="s">
-        <v>230</v>
+        <v>175</v>
       </c>
       <c r="F34" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="G34" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="H34" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="B35" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="C35" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="D35" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E35" t="s">
-        <v>237</v>
+        <v>175</v>
       </c>
       <c r="F35" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="G35" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="H35" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="B36" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="C36" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>244</v>
+        <v>175</v>
       </c>
       <c r="F36" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="G36" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="H36" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="B37" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="C37" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="D37" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E37" t="s">
-        <v>251</v>
+        <v>175</v>
       </c>
       <c r="F37" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="G37" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="H37" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="B38" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="C38" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="D38" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>258</v>
+        <v>175</v>
       </c>
       <c r="F38" t="s">
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="G38" t="s">
-        <v>260</v>
+        <v>231</v>
       </c>
       <c r="H38" t="s">
-        <v>261</v>
+        <v>232</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="B39" t="s">
-        <v>263</v>
+        <v>234</v>
       </c>
       <c r="C39" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="D39" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E39" t="s">
-        <v>265</v>
+        <v>175</v>
       </c>
       <c r="F39" t="s">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="G39" t="s">
-        <v>267</v>
+        <v>237</v>
       </c>
       <c r="H39" t="s">
-        <v>268</v>
+        <v>238</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>269</v>
+        <v>239</v>
       </c>
       <c r="B40" t="s">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="C40" t="s">
-        <v>271</v>
+        <v>241</v>
       </c>
       <c r="D40" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E40" t="s">
-        <v>272</v>
+        <v>175</v>
       </c>
       <c r="F40" t="s">
-        <v>273</v>
+        <v>242</v>
       </c>
       <c r="G40" t="s">
-        <v>274</v>
+        <v>243</v>
       </c>
       <c r="H40" t="s">
-        <v>275</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>276</v>
+        <v>245</v>
       </c>
       <c r="B41" t="s">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="C41" t="s">
-        <v>278</v>
+        <v>247</v>
       </c>
       <c r="D41" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E41" t="s">
-        <v>279</v>
+        <v>175</v>
       </c>
       <c r="F41" t="s">
-        <v>280</v>
+        <v>248</v>
       </c>
       <c r="G41" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="H41" t="s">
-        <v>282</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
       <c r="B42" t="s">
-        <v>284</v>
+        <v>252</v>
       </c>
       <c r="C42" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E42" t="s">
-        <v>286</v>
+        <v>175</v>
       </c>
       <c r="F42" t="s">
-        <v>287</v>
+        <v>254</v>
       </c>
       <c r="G42" t="s">
-        <v>288</v>
+        <v>255</v>
       </c>
       <c r="H42" t="s">
-        <v>289</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>290</v>
+        <v>257</v>
       </c>
       <c r="B43" t="s">
-        <v>291</v>
+        <v>258</v>
       </c>
       <c r="C43" t="s">
-        <v>292</v>
+        <v>259</v>
       </c>
       <c r="D43" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E43" t="s">
-        <v>293</v>
+        <v>175</v>
       </c>
       <c r="F43" t="s">
-        <v>294</v>
+        <v>260</v>
       </c>
       <c r="G43" t="s">
-        <v>295</v>
+        <v>261</v>
       </c>
       <c r="H43" t="s">
-        <v>296</v>
+        <v>262</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>297</v>
+        <v>263</v>
       </c>
       <c r="B44" t="s">
-        <v>298</v>
+        <v>264</v>
       </c>
       <c r="C44" t="s">
-        <v>299</v>
+        <v>265</v>
       </c>
       <c r="D44" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E44" t="s">
-        <v>300</v>
+        <v>175</v>
       </c>
       <c r="F44" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="G44" t="s">
-        <v>302</v>
+        <v>267</v>
       </c>
       <c r="H44" t="s">
-        <v>303</v>
+        <v>268</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="B45" t="s">
-        <v>305</v>
+        <v>270</v>
       </c>
       <c r="C45" t="s">
-        <v>306</v>
+        <v>271</v>
       </c>
       <c r="D45" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E45" t="s">
-        <v>307</v>
+        <v>175</v>
       </c>
       <c r="F45" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="G45" t="s">
-        <v>309</v>
+        <v>273</v>
       </c>
       <c r="H45" t="s">
-        <v>310</v>
+        <v>274</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>311</v>
+        <v>275</v>
       </c>
       <c r="B46" t="s">
-        <v>312</v>
+        <v>276</v>
       </c>
       <c r="C46" t="s">
-        <v>313</v>
+        <v>277</v>
       </c>
       <c r="D46" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E46" t="s">
-        <v>314</v>
+        <v>175</v>
       </c>
       <c r="F46" t="s">
-        <v>315</v>
+        <v>278</v>
       </c>
       <c r="G46" t="s">
-        <v>316</v>
+        <v>279</v>
       </c>
       <c r="H46" t="s">
-        <v>317</v>
+        <v>280</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>318</v>
+        <v>281</v>
       </c>
       <c r="B47" t="s">
-        <v>319</v>
+        <v>282</v>
       </c>
       <c r="C47" t="s">
-        <v>320</v>
+        <v>283</v>
       </c>
       <c r="D47" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E47" t="s">
-        <v>321</v>
+        <v>175</v>
       </c>
       <c r="F47" t="s">
-        <v>322</v>
+        <v>284</v>
       </c>
       <c r="G47" t="s">
-        <v>323</v>
+        <v>285</v>
       </c>
       <c r="H47" t="s">
-        <v>324</v>
+        <v>286</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>325</v>
+        <v>287</v>
       </c>
       <c r="B48" t="s">
-        <v>326</v>
+        <v>288</v>
       </c>
       <c r="C48" t="s">
-        <v>327</v>
+        <v>289</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E48" t="s">
-        <v>328</v>
+        <v>175</v>
       </c>
       <c r="F48" t="s">
-        <v>329</v>
+        <v>290</v>
       </c>
       <c r="G48" t="s">
-        <v>330</v>
+        <v>291</v>
       </c>
       <c r="H48" t="s">
-        <v>331</v>
+        <v>292</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>332</v>
+        <v>293</v>
       </c>
       <c r="B49" t="s">
-        <v>333</v>
+        <v>294</v>
       </c>
       <c r="C49" t="s">
-        <v>334</v>
+        <v>295</v>
       </c>
       <c r="D49" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E49" t="s">
-        <v>335</v>
+        <v>175</v>
       </c>
       <c r="F49" t="s">
-        <v>336</v>
+        <v>296</v>
       </c>
       <c r="G49" t="s">
-        <v>337</v>
+        <v>297</v>
       </c>
       <c r="H49" t="s">
-        <v>338</v>
+        <v>298</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>339</v>
+        <v>299</v>
       </c>
       <c r="B50" t="s">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="C50" t="s">
-        <v>341</v>
+        <v>301</v>
       </c>
       <c r="D50" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E50" t="s">
-        <v>342</v>
+        <v>175</v>
       </c>
       <c r="F50" t="s">
-        <v>343</v>
+        <v>302</v>
       </c>
       <c r="G50" t="s">
-        <v>344</v>
+        <v>303</v>
       </c>
       <c r="H50" t="s">
-        <v>345</v>
+        <v>304</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>346</v>
+        <v>305</v>
       </c>
       <c r="B51" t="s">
-        <v>347</v>
+        <v>306</v>
       </c>
       <c r="C51" t="s">
-        <v>348</v>
+        <v>307</v>
       </c>
       <c r="D51" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E51" t="s">
-        <v>349</v>
+        <v>175</v>
       </c>
       <c r="F51" t="s">
-        <v>350</v>
+        <v>308</v>
       </c>
       <c r="G51" t="s">
-        <v>351</v>
+        <v>309</v>
       </c>
       <c r="H51" t="s">
-        <v>352</v>
+        <v>310</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>353</v>
+        <v>311</v>
       </c>
       <c r="B52" t="s">
-        <v>354</v>
+        <v>312</v>
       </c>
       <c r="C52" t="s">
-        <v>355</v>
+        <v>313</v>
       </c>
       <c r="D52" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E52" t="s">
-        <v>356</v>
+        <v>175</v>
       </c>
       <c r="F52" t="s">
-        <v>357</v>
+        <v>314</v>
       </c>
       <c r="G52" t="s">
-        <v>358</v>
+        <v>315</v>
       </c>
       <c r="H52" t="s">
-        <v>359</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>360</v>
+        <v>317</v>
       </c>
       <c r="B53" t="s">
-        <v>361</v>
+        <v>318</v>
       </c>
       <c r="C53" t="s">
-        <v>362</v>
+        <v>319</v>
       </c>
       <c r="D53" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E53" t="s">
-        <v>363</v>
+        <v>175</v>
       </c>
       <c r="F53" t="s">
-        <v>364</v>
+        <v>320</v>
       </c>
       <c r="G53" t="s">
-        <v>365</v>
+        <v>321</v>
       </c>
       <c r="H53" t="s">
-        <v>366</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>367</v>
+        <v>323</v>
       </c>
       <c r="B54" t="s">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="C54" t="s">
-        <v>369</v>
+        <v>325</v>
       </c>
       <c r="D54" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E54" t="s">
-        <v>370</v>
+        <v>175</v>
       </c>
       <c r="F54" t="s">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="G54" t="s">
-        <v>372</v>
+        <v>327</v>
       </c>
       <c r="H54" t="s">
-        <v>373</v>
+        <v>328</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>374</v>
+        <v>329</v>
       </c>
       <c r="B55" t="s">
-        <v>375</v>
+        <v>330</v>
       </c>
       <c r="C55" t="s">
-        <v>376</v>
+        <v>331</v>
       </c>
       <c r="D55" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E55" t="s">
-        <v>377</v>
+        <v>175</v>
       </c>
       <c r="F55" t="s">
-        <v>378</v>
+        <v>332</v>
       </c>
       <c r="G55" t="s">
-        <v>379</v>
+        <v>333</v>
       </c>
       <c r="H55" t="s">
-        <v>380</v>
+        <v>334</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>335</v>
+      </c>
+      <c r="B56" t="s">
+        <v>336</v>
+      </c>
+      <c r="C56" t="s">
+        <v>337</v>
+      </c>
+      <c r="D56" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" t="s">
+        <v>338</v>
+      </c>
+      <c r="F56" t="s">
+        <v>339</v>
+      </c>
+      <c r="G56" t="s">
+        <v>340</v>
+      </c>
+      <c r="H56" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>342</v>
+      </c>
+      <c r="B57" t="s">
+        <v>343</v>
+      </c>
+      <c r="C57" t="s">
+        <v>344</v>
+      </c>
+      <c r="D57" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" t="s">
+        <v>338</v>
+      </c>
+      <c r="F57" t="s">
+        <v>345</v>
+      </c>
+      <c r="G57" t="s">
+        <v>346</v>
+      </c>
+      <c r="H57" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>348</v>
+      </c>
+      <c r="B58" t="s">
+        <v>349</v>
+      </c>
+      <c r="C58" t="s">
+        <v>350</v>
+      </c>
+      <c r="D58" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" t="s">
+        <v>338</v>
+      </c>
+      <c r="F58" t="s">
+        <v>351</v>
+      </c>
+      <c r="G58" t="s">
+        <v>352</v>
+      </c>
+      <c r="H58" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>354</v>
+      </c>
+      <c r="B59" t="s">
+        <v>355</v>
+      </c>
+      <c r="C59" t="s">
+        <v>356</v>
+      </c>
+      <c r="D59" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" t="s">
+        <v>338</v>
+      </c>
+      <c r="F59" t="s">
+        <v>357</v>
+      </c>
+      <c r="G59" t="s">
+        <v>358</v>
+      </c>
+      <c r="H59" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>360</v>
+      </c>
+      <c r="B60" t="s">
+        <v>361</v>
+      </c>
+      <c r="C60" t="s">
+        <v>362</v>
+      </c>
+      <c r="D60" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" t="s">
+        <v>338</v>
+      </c>
+      <c r="F60" t="s">
+        <v>363</v>
+      </c>
+      <c r="G60" t="s">
+        <v>364</v>
+      </c>
+      <c r="H60" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>366</v>
+      </c>
+      <c r="B61" t="s">
+        <v>367</v>
+      </c>
+      <c r="C61" t="s">
+        <v>368</v>
+      </c>
+      <c r="D61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" t="s">
+        <v>338</v>
+      </c>
+      <c r="F61" t="s">
+        <v>369</v>
+      </c>
+      <c r="G61" t="s">
+        <v>370</v>
+      </c>
+      <c r="H61" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>372</v>
+      </c>
+      <c r="B62" t="s">
+        <v>373</v>
+      </c>
+      <c r="C62" t="s">
+        <v>374</v>
+      </c>
+      <c r="D62" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" t="s">
+        <v>338</v>
+      </c>
+      <c r="F62" t="s">
+        <v>375</v>
+      </c>
+      <c r="G62" t="s">
+        <v>376</v>
+      </c>
+      <c r="H62" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>378</v>
+      </c>
+      <c r="B63" t="s">
+        <v>379</v>
+      </c>
+      <c r="C63" t="s">
+        <v>380</v>
+      </c>
+      <c r="D63" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" t="s">
+        <v>338</v>
+      </c>
+      <c r="F63" t="s">
         <v>381</v>
       </c>
-      <c r="B56" t="s">
+      <c r="G63" t="s">
         <v>382</v>
       </c>
-      <c r="C56" t="s">
+      <c r="H63" t="s">
         <v>383</v>
       </c>
-      <c r="D56" t="s">
-        <v>13</v>
-      </c>
-      <c r="E56" t="s">
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
         <v>384</v>
       </c>
-      <c r="F56" t="s">
+      <c r="B64" t="s">
         <v>385</v>
       </c>
-      <c r="G56" t="s">
+      <c r="C64" t="s">
         <v>386</v>
       </c>
-      <c r="H56" t="s">
+      <c r="D64" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" t="s">
+        <v>338</v>
+      </c>
+      <c r="F64" t="s">
         <v>387</v>
+      </c>
+      <c r="G64" t="s">
+        <v>388</v>
+      </c>
+      <c r="H64" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>390</v>
+      </c>
+      <c r="B65" t="s">
+        <v>391</v>
+      </c>
+      <c r="C65" t="s">
+        <v>392</v>
+      </c>
+      <c r="D65" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" t="s">
+        <v>338</v>
+      </c>
+      <c r="F65" t="s">
+        <v>393</v>
+      </c>
+      <c r="G65" t="s">
+        <v>394</v>
+      </c>
+      <c r="H65" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>396</v>
+      </c>
+      <c r="B66" t="s">
+        <v>397</v>
+      </c>
+      <c r="C66" t="s">
+        <v>398</v>
+      </c>
+      <c r="D66" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" t="s">
+        <v>338</v>
+      </c>
+      <c r="F66" t="s">
+        <v>399</v>
+      </c>
+      <c r="G66" t="s">
+        <v>400</v>
+      </c>
+      <c r="H66" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>402</v>
+      </c>
+      <c r="B67" t="s">
+        <v>403</v>
+      </c>
+      <c r="C67" t="s">
+        <v>404</v>
+      </c>
+      <c r="D67" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" t="s">
+        <v>338</v>
+      </c>
+      <c r="F67" t="s">
+        <v>405</v>
+      </c>
+      <c r="G67" t="s">
+        <v>406</v>
+      </c>
+      <c r="H67" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>408</v>
+      </c>
+      <c r="B68" t="s">
+        <v>409</v>
+      </c>
+      <c r="C68" t="s">
+        <v>410</v>
+      </c>
+      <c r="D68" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" t="s">
+        <v>338</v>
+      </c>
+      <c r="F68" t="s">
+        <v>411</v>
+      </c>
+      <c r="G68" t="s">
+        <v>412</v>
+      </c>
+      <c r="H68" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>414</v>
+      </c>
+      <c r="B69" t="s">
+        <v>415</v>
+      </c>
+      <c r="C69" t="s">
+        <v>416</v>
+      </c>
+      <c r="D69" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" t="s">
+        <v>338</v>
+      </c>
+      <c r="F69" t="s">
+        <v>417</v>
+      </c>
+      <c r="G69" t="s">
+        <v>418</v>
+      </c>
+      <c r="H69" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>420</v>
+      </c>
+      <c r="B70" t="s">
+        <v>421</v>
+      </c>
+      <c r="C70" t="s">
+        <v>422</v>
+      </c>
+      <c r="D70" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" t="s">
+        <v>338</v>
+      </c>
+      <c r="F70" t="s">
+        <v>423</v>
+      </c>
+      <c r="G70" t="s">
+        <v>424</v>
+      </c>
+      <c r="H70" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>426</v>
+      </c>
+      <c r="B71" t="s">
+        <v>427</v>
+      </c>
+      <c r="C71" t="s">
+        <v>428</v>
+      </c>
+      <c r="D71" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" t="s">
+        <v>338</v>
+      </c>
+      <c r="F71" t="s">
+        <v>429</v>
+      </c>
+      <c r="G71" t="s">
+        <v>430</v>
+      </c>
+      <c r="H71" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>432</v>
+      </c>
+      <c r="B72" t="s">
+        <v>433</v>
+      </c>
+      <c r="C72" t="s">
+        <v>434</v>
+      </c>
+      <c r="D72" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" t="s">
+        <v>338</v>
+      </c>
+      <c r="F72" t="s">
+        <v>435</v>
+      </c>
+      <c r="G72" t="s">
+        <v>436</v>
+      </c>
+      <c r="H72" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>438</v>
+      </c>
+      <c r="B73" t="s">
+        <v>439</v>
+      </c>
+      <c r="C73" t="s">
+        <v>440</v>
+      </c>
+      <c r="D73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" t="s">
+        <v>338</v>
+      </c>
+      <c r="F73" t="s">
+        <v>441</v>
+      </c>
+      <c r="G73" t="s">
+        <v>442</v>
+      </c>
+      <c r="H73" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>444</v>
+      </c>
+      <c r="B74" t="s">
+        <v>445</v>
+      </c>
+      <c r="C74" t="s">
+        <v>446</v>
+      </c>
+      <c r="D74" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" t="s">
+        <v>338</v>
+      </c>
+      <c r="F74" t="s">
+        <v>447</v>
+      </c>
+      <c r="G74" t="s">
+        <v>448</v>
+      </c>
+      <c r="H74" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>450</v>
+      </c>
+      <c r="B75" t="s">
+        <v>451</v>
+      </c>
+      <c r="C75" t="s">
+        <v>452</v>
+      </c>
+      <c r="D75" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" t="s">
+        <v>338</v>
+      </c>
+      <c r="F75" t="s">
+        <v>453</v>
+      </c>
+      <c r="G75" t="s">
+        <v>454</v>
+      </c>
+      <c r="H75" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>456</v>
+      </c>
+      <c r="B76" t="s">
+        <v>457</v>
+      </c>
+      <c r="C76" t="s">
+        <v>458</v>
+      </c>
+      <c r="D76" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" t="s">
+        <v>338</v>
+      </c>
+      <c r="F76" t="s">
+        <v>459</v>
+      </c>
+      <c r="G76" t="s">
+        <v>460</v>
+      </c>
+      <c r="H76" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>462</v>
+      </c>
+      <c r="B77" t="s">
+        <v>463</v>
+      </c>
+      <c r="C77" t="s">
+        <v>464</v>
+      </c>
+      <c r="D77" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" t="s">
+        <v>338</v>
+      </c>
+      <c r="F77" t="s">
+        <v>465</v>
+      </c>
+      <c r="G77" t="s">
+        <v>466</v>
+      </c>
+      <c r="H77" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>468</v>
+      </c>
+      <c r="B78" t="s">
+        <v>469</v>
+      </c>
+      <c r="C78" t="s">
+        <v>470</v>
+      </c>
+      <c r="D78" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" t="s">
+        <v>338</v>
+      </c>
+      <c r="F78" t="s">
+        <v>471</v>
+      </c>
+      <c r="G78" t="s">
+        <v>472</v>
+      </c>
+      <c r="H78" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>474</v>
+      </c>
+      <c r="B79" t="s">
+        <v>475</v>
+      </c>
+      <c r="C79" t="s">
+        <v>476</v>
+      </c>
+      <c r="D79" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" t="s">
+        <v>338</v>
+      </c>
+      <c r="F79" t="s">
+        <v>477</v>
+      </c>
+      <c r="G79" t="s">
+        <v>478</v>
+      </c>
+      <c r="H79" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>480</v>
+      </c>
+      <c r="B80" t="s">
+        <v>481</v>
+      </c>
+      <c r="C80" t="s">
+        <v>482</v>
+      </c>
+      <c r="D80" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" t="s">
+        <v>338</v>
+      </c>
+      <c r="F80" t="s">
+        <v>483</v>
+      </c>
+      <c r="G80" t="s">
+        <v>484</v>
+      </c>
+      <c r="H80" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>486</v>
+      </c>
+      <c r="B81" t="s">
+        <v>487</v>
+      </c>
+      <c r="C81" t="s">
+        <v>488</v>
+      </c>
+      <c r="D81" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" t="s">
+        <v>338</v>
+      </c>
+      <c r="F81" t="s">
+        <v>489</v>
+      </c>
+      <c r="G81" t="s">
+        <v>490</v>
+      </c>
+      <c r="H81" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>492</v>
+      </c>
+      <c r="B82" t="s">
+        <v>493</v>
+      </c>
+      <c r="C82" t="s">
+        <v>494</v>
+      </c>
+      <c r="D82" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" t="s">
+        <v>338</v>
+      </c>
+      <c r="F82" t="s">
+        <v>495</v>
+      </c>
+      <c r="G82" t="s">
+        <v>496</v>
+      </c>
+      <c r="H82" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>498</v>
+      </c>
+      <c r="B83" t="s">
+        <v>499</v>
+      </c>
+      <c r="C83" t="s">
+        <v>500</v>
+      </c>
+      <c r="D83" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" t="s">
+        <v>338</v>
+      </c>
+      <c r="F83" t="s">
+        <v>501</v>
+      </c>
+      <c r="G83" t="s">
+        <v>502</v>
+      </c>
+      <c r="H83" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>504</v>
+      </c>
+      <c r="B84" t="s">
+        <v>505</v>
+      </c>
+      <c r="C84" t="s">
+        <v>506</v>
+      </c>
+      <c r="D84" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" t="s">
+        <v>338</v>
+      </c>
+      <c r="F84" t="s">
+        <v>507</v>
+      </c>
+      <c r="G84" t="s">
+        <v>508</v>
+      </c>
+      <c r="H84" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>510</v>
+      </c>
+      <c r="B85" t="s">
+        <v>511</v>
+      </c>
+      <c r="C85" t="s">
+        <v>512</v>
+      </c>
+      <c r="D85" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" t="s">
+        <v>338</v>
+      </c>
+      <c r="F85" t="s">
+        <v>513</v>
+      </c>
+      <c r="G85" t="s">
+        <v>514</v>
+      </c>
+      <c r="H85" t="s">
+        <v>515</v>
       </c>
     </row>
   </sheetData>
